--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AE877A-21A3-49D5-9151-10ECE7F69722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568CB4D5-7DF2-4372-B397-C5170D239414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="263">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1029,6 +1029,67 @@
     <t>ReallyDeleteSavePanel内</t>
     <rPh sb="21" eb="22">
       <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>彷徨う者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wanderer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徘徊者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Silencio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Errante</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>彷徨う者関連パネルを開くボタン</t>
+    <rPh sb="4" eb="6">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アーカイブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Archive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>归档</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歸檔</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>archivo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>arquivo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アーカイブパネルを開くボタン</t>
+    <rPh sb="9" eb="10">
+      <t>ヒラ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1411,7 +1472,7 @@
     <col min="11" max="11" width="21.75" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="24.375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="29.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3933,22 +3994,88 @@
       <c r="A60">
         <v>58</v>
       </c>
+      <c r="B60" t="s">
+        <v>250</v>
+      </c>
       <c r="C60">
         <v>14</v>
       </c>
+      <c r="D60" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="E60">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G60" s="2">
+        <v>14</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I60" s="5">
+        <v>14</v>
+      </c>
+      <c r="J60" t="s">
+        <v>253</v>
+      </c>
+      <c r="K60">
+        <v>12</v>
+      </c>
+      <c r="L60" t="s">
+        <v>254</v>
+      </c>
+      <c r="M60">
+        <v>12</v>
+      </c>
+      <c r="N60" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61">
         <v>59</v>
       </c>
+      <c r="B61" t="s">
+        <v>256</v>
+      </c>
       <c r="C61">
         <v>14</v>
       </c>
+      <c r="D61" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="E61">
         <v>14</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="G61" s="2">
+        <v>14</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="I61" s="2">
+        <v>14</v>
+      </c>
+      <c r="J61" t="s">
+        <v>260</v>
+      </c>
+      <c r="K61" s="2">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
+        <v>261</v>
+      </c>
+      <c r="M61" s="2">
+        <v>14</v>
+      </c>
+      <c r="N61" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:14">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568CB4D5-7DF2-4372-B397-C5170D239414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0F614-7192-4A12-82F0-B48F03FEC8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1560,7 +1560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="37.5">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="37.5">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="37.5">
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="37.5">
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="37.5">
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="37.5">
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3998,37 +3998,37 @@
         <v>250</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>251</v>
       </c>
       <c r="E60">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>252</v>
       </c>
       <c r="G60" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>252</v>
       </c>
       <c r="I60" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J60" t="s">
         <v>253</v>
       </c>
       <c r="K60">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L60" t="s">
         <v>254</v>
       </c>
       <c r="M60">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N60" t="s">
         <v>255</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB0F614-7192-4A12-82F0-B48F03FEC8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4987498D-AFA4-41B7-AE58-ED1651F54FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="269">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1091,6 +1091,30 @@
     <rPh sb="9" eb="10">
       <t>ヒラ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リタイア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PausePanel内</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Retire</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>退休</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Retirarse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aposentar</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4082,11 +4106,44 @@
       <c r="A62">
         <v>60</v>
       </c>
+      <c r="B62" t="s">
+        <v>263</v>
+      </c>
       <c r="C62">
         <v>14</v>
       </c>
+      <c r="D62" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="E62">
         <v>14</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G62">
+        <v>14</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="I62">
+        <v>14</v>
+      </c>
+      <c r="J62" t="s">
+        <v>267</v>
+      </c>
+      <c r="K62">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>268</v>
+      </c>
+      <c r="M62">
+        <v>14</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="63" spans="1:14">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4987498D-AFA4-41B7-AE58-ED1651F54FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D990137F-6C09-4796-9ED4-8808AECE754A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="275">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -309,13 +309,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ReturnToTitlePanel内</t>
-    <rPh sb="18" eb="19">
-      <t>ナイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BrightnessAdjustmentPanel内</t>
     <rPh sb="25" eb="26">
       <t>ナイ</t>
@@ -1115,6 +1108,37 @@
   </si>
   <si>
     <t>Aposentar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ選択へ戻る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Return to stage selection</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返回关卡选择</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>返回關卡選擇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Volver a la selección de escenario</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Voltar à seleção de cenário</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ReturnToTitlePanel内とReturnToSelectStagePanel内</t>
+    <rPh sb="18" eb="19">
+      <t>ナイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1492,9 +1516,9 @@
     <col min="7" max="7" width="24.875" customWidth="1"/>
     <col min="8" max="8" width="22.25" customWidth="1"/>
     <col min="9" max="9" width="22.5" customWidth="1"/>
-    <col min="10" max="10" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="32.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.75" customWidth="1"/>
-    <col min="12" max="12" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="26" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="29.25" style="1" customWidth="1"/>
   </cols>
@@ -1516,28 +1540,28 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" t="s">
         <v>134</v>
       </c>
-      <c r="G1" t="s">
-        <v>135</v>
-      </c>
       <c r="H1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1" t="s">
         <v>164</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>165</v>
       </c>
-      <c r="J1" t="s">
-        <v>166</v>
-      </c>
       <c r="K1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>49</v>
@@ -1560,25 +1584,25 @@
         <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G2" s="2">
         <v>14</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I2" s="5">
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K2">
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M2">
         <v>14</v>
@@ -1601,31 +1625,31 @@
         <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I3" s="5">
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K3">
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M3">
         <v>14</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1645,25 +1669,25 @@
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
         <v>14</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I4" s="5">
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K4">
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M4">
         <v>14</v>
@@ -1686,25 +1710,25 @@
         <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G5" s="2">
         <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" s="5">
         <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K5">
         <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M5">
         <v>24</v>
@@ -1730,25 +1754,25 @@
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G6" s="2">
         <v>14</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I6" s="5">
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K6">
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -1774,7 +1798,7 @@
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" s="2">
         <v>14</v>
@@ -1850,31 +1874,31 @@
         <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9">
         <v>12</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G9" s="2">
         <v>12</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I9" s="5">
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K9">
         <v>12</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M9">
         <v>12</v>
@@ -1897,25 +1921,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G10" s="2">
         <v>10</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I10" s="5">
         <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1932,31 +1956,31 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>16</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G11" s="2">
         <v>16</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I11" s="5">
         <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K11">
         <v>12</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M11">
         <v>12</v>
@@ -1979,25 +2003,25 @@
         <v>16</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" s="2">
         <v>16</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I12" s="5">
         <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K12">
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M12">
         <v>16</v>
@@ -2020,25 +2044,25 @@
         <v>10</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G13" s="2">
         <v>10</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I13" s="5">
         <v>10</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -2061,25 +2085,25 @@
         <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" s="2">
         <v>10</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I14" s="5">
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K14">
         <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -2105,31 +2129,31 @@
         <v>16</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" s="2">
         <v>16</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I15" s="5">
         <v>16</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K15">
         <v>14</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M15">
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2149,31 +2173,31 @@
         <v>16</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G16" s="2">
         <v>16</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I16" s="5">
         <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K16">
         <v>14</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M16">
         <v>14</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="37.5">
@@ -2193,25 +2217,25 @@
         <v>10</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G17" s="2">
         <v>10</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I17" s="5">
         <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -2228,31 +2252,31 @@
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G18" s="2">
         <v>10</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I18" s="5">
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2263,37 +2287,37 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E19">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G19" s="2">
         <v>16</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I19" s="5">
         <v>16</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K19">
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M19">
         <v>16</v>
@@ -2316,25 +2340,25 @@
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" s="2">
         <v>16</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I20" s="5">
         <v>16</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K20">
         <v>16</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M20">
         <v>16</v>
@@ -2357,25 +2381,25 @@
         <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" s="2">
         <v>24</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I21" s="5">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K21">
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M21">
         <v>18</v>
@@ -2401,25 +2425,25 @@
         <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G22" s="2">
         <v>24</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I22" s="5">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K22">
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M22">
         <v>18</v>
@@ -2445,25 +2469,25 @@
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G23" s="2">
         <v>24</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I23" s="5">
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K23">
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M23">
         <v>18</v>
@@ -2489,25 +2513,25 @@
         <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24" s="2">
         <v>24</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I24" s="5">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K24">
         <v>18</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M24">
         <v>18</v>
@@ -2530,25 +2554,25 @@
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G25" s="2">
         <v>24</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I25" s="5">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K25">
         <v>18</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M25">
         <v>18</v>
@@ -2571,25 +2595,25 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G26" s="2">
         <v>24</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I26" s="5">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K26">
         <v>18</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M26">
         <v>18</v>
@@ -2612,25 +2636,25 @@
         <v>32</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G27" s="2">
         <v>32</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I27" s="5">
         <v>32</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K27">
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M27">
         <v>32</v>
@@ -2656,25 +2680,25 @@
         <v>32</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G28" s="2">
         <v>32</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I28" s="5">
         <v>32</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K28">
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M28">
         <v>32</v>
@@ -2683,7 +2707,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2700,34 +2724,34 @@
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G29" s="2">
         <v>14</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I29" s="5">
         <v>14</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K29">
         <v>14</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M29">
         <v>14</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="37.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2744,31 +2768,31 @@
         <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G30" s="2">
         <v>14</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I30" s="5">
         <v>14</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K30">
         <v>14</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M30">
         <v>14</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2788,31 +2812,31 @@
         <v>12</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2">
         <v>12</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I31" s="5">
         <v>12</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K31">
         <v>12</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M31">
         <v>12</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2820,43 +2844,43 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C32">
-        <v>14</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32">
+        <v>14</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="2">
+        <v>14</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I32" s="5">
+        <v>14</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K32">
+        <v>14</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M32">
+        <v>14</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E32">
-        <v>14</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="2">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="I32" s="5">
-        <v>14</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K32">
-        <v>14</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="M32">
-        <v>14</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="75">
@@ -2876,31 +2900,31 @@
         <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G33" s="2">
         <v>14</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I33" s="5">
         <v>14</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K33">
         <v>14</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M33">
         <v>14</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2908,43 +2932,43 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34">
         <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E34">
         <v>14</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G34" s="2">
         <v>14</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>14</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K34">
         <v>12</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M34">
         <v>14</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2952,43 +2976,43 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35">
+        <v>14</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="2">
+        <v>14</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35" s="5">
+        <v>14</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="K35">
+        <v>14</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="M35">
+        <v>14</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E35">
-        <v>14</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G35" s="2">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I35" s="5">
-        <v>14</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K35">
-        <v>14</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="M35">
-        <v>14</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2996,43 +3020,43 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36">
         <v>14</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G36" s="2">
         <v>14</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I36" s="5">
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K36">
         <v>12</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M36">
         <v>12</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="37.5">
@@ -3040,43 +3064,43 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37">
+        <v>14</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C37">
-        <v>14</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E37">
         <v>14</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G37" s="2">
         <v>14</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I37" s="5">
         <v>14</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K37">
         <v>14</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M37">
         <v>14</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="37.5">
@@ -3084,43 +3108,43 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38">
         <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38">
         <v>16</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2">
         <v>20</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I38" s="5">
         <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K38">
         <v>12</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M38">
         <v>12</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -3128,37 +3152,37 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E39">
         <v>14</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G39" s="2">
         <v>14</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I39" s="5">
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K39">
         <v>14</v>
       </c>
       <c r="L39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M39">
         <v>14</v>
@@ -3169,37 +3193,37 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C40">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E40">
         <v>14</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G40" s="2">
         <v>14</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I40" s="5">
         <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K40">
         <v>14</v>
       </c>
       <c r="L40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M40">
         <v>14</v>
@@ -3210,37 +3234,37 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C41">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G41" s="2">
         <v>14</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I41" s="5">
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K41">
         <v>14</v>
       </c>
       <c r="L41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M41">
         <v>14</v>
@@ -3251,7 +3275,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>20</v>
@@ -3263,31 +3287,31 @@
         <v>16</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G42" s="2">
         <v>20</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I42" s="5">
         <v>20</v>
       </c>
       <c r="J42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K42">
         <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M42">
         <v>16</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -3295,43 +3319,43 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43">
+        <v>14</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G43" s="2">
+        <v>14</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I43" s="5">
+        <v>14</v>
+      </c>
+      <c r="J43" t="s">
+        <v>195</v>
+      </c>
+      <c r="K43">
+        <v>14</v>
+      </c>
+      <c r="L43" t="s">
+        <v>195</v>
+      </c>
+      <c r="M43">
+        <v>14</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C43">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43">
-        <v>14</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G43" s="2">
-        <v>14</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I43" s="5">
-        <v>14</v>
-      </c>
-      <c r="J43" t="s">
-        <v>196</v>
-      </c>
-      <c r="K43">
-        <v>14</v>
-      </c>
-      <c r="L43" t="s">
-        <v>196</v>
-      </c>
-      <c r="M43">
-        <v>14</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -3339,43 +3363,43 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>20</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G44" s="2">
         <v>20</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>20</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K44">
         <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M44">
         <v>20</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="37.5">
@@ -3383,37 +3407,37 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E45">
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G45" s="2">
         <v>10</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I45" s="5">
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K45">
         <v>8</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M45">
         <v>8</v>
@@ -3424,37 +3448,37 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C46">
         <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E46">
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G46" s="2">
         <v>10</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K46">
         <v>8</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M46">
         <v>8</v>
@@ -3477,31 +3501,31 @@
         <v>16</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G47" s="2">
         <v>16</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I47" s="5">
         <v>16</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K47">
         <v>16</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M47">
         <v>16</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="37.5">
@@ -3521,31 +3545,31 @@
         <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G48" s="2">
         <v>16</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I48" s="5">
         <v>16</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K48">
         <v>16</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M48">
         <v>16</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="37.5">
@@ -3565,31 +3589,31 @@
         <v>16</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G49" s="2">
         <v>16</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I49" s="5">
         <v>16</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K49">
         <v>14</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M49">
         <v>14</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="37.5">
@@ -3609,31 +3633,31 @@
         <v>16</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G50" s="2">
         <v>16</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I50" s="5">
         <v>16</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K50">
         <v>14</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M50">
         <v>14</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3641,37 +3665,37 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51">
         <v>14</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E51">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G51">
         <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I51">
         <v>14</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K51">
         <v>14</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M51">
         <v>14</v>
@@ -3682,37 +3706,37 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C52">
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E52">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G52">
         <v>14</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I52">
         <v>14</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K52">
         <v>14</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M52">
         <v>14</v>
@@ -3723,37 +3747,37 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G53">
         <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I53">
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K53">
         <v>14</v>
       </c>
       <c r="L53" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M53">
         <v>14</v>
@@ -3764,37 +3788,37 @@
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C54">
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E54">
         <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G54">
         <v>14</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I54">
         <v>14</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K54">
         <v>14</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M54">
         <v>14</v>
@@ -3805,37 +3829,37 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>235</v>
+      </c>
+      <c r="C55">
+        <v>14</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C55">
-        <v>14</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55">
+        <v>14</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E55">
-        <v>14</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
         <v>238</v>
       </c>
-      <c r="G55">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="I55">
+        <v>14</v>
+      </c>
+      <c r="J55" t="s">
         <v>239</v>
       </c>
-      <c r="I55">
-        <v>14</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="K55">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
         <v>240</v>
-      </c>
-      <c r="K55">
-        <v>14</v>
-      </c>
-      <c r="L55" t="s">
-        <v>241</v>
       </c>
       <c r="M55">
         <v>14</v>
@@ -3858,31 +3882,31 @@
         <v>24</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G56" s="2">
         <v>24</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I56" s="5">
         <v>24</v>
       </c>
       <c r="J56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K56">
         <v>24</v>
       </c>
       <c r="L56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M56">
         <v>24</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3890,37 +3914,37 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>243</v>
+      </c>
+      <c r="C57">
+        <v>14</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E57">
+        <v>14</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C57">
-        <v>14</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57">
-        <v>14</v>
-      </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
         <v>245</v>
       </c>
-      <c r="G57">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
         <v>246</v>
-      </c>
-      <c r="I57">
-        <v>14</v>
-      </c>
-      <c r="J57" t="s">
-        <v>247</v>
       </c>
       <c r="K57">
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M57">
         <v>12</v>
@@ -3943,31 +3967,31 @@
         <v>14</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G58" s="2">
         <v>14</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I58" s="5">
         <v>14</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K58">
         <v>14</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M58">
         <v>14</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3987,31 +4011,31 @@
         <v>14</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G59" s="2">
         <v>14</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I59" s="5">
         <v>14</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K59">
         <v>14</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M59">
         <v>14</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -4019,43 +4043,43 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>249</v>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C60">
-        <v>16</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E60">
-        <v>16</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2">
+        <v>16</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="I60" s="5">
+        <v>16</v>
+      </c>
+      <c r="J60" t="s">
         <v>252</v>
       </c>
-      <c r="G60" s="2">
-        <v>16</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="I60" s="5">
-        <v>16</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="K60">
+        <v>16</v>
+      </c>
+      <c r="L60" t="s">
         <v>253</v>
       </c>
-      <c r="K60">
-        <v>16</v>
-      </c>
-      <c r="L60" t="s">
+      <c r="M60">
+        <v>16</v>
+      </c>
+      <c r="N60" t="s">
         <v>254</v>
-      </c>
-      <c r="M60">
-        <v>16</v>
-      </c>
-      <c r="N60" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -4063,43 +4087,43 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>255</v>
+      </c>
+      <c r="C61">
+        <v>14</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C61">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61">
+        <v>14</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="E61">
-        <v>14</v>
-      </c>
-      <c r="F61" s="8" t="s">
+      <c r="G61" s="2">
+        <v>14</v>
+      </c>
+      <c r="H61" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G61" s="2">
-        <v>14</v>
-      </c>
-      <c r="H61" s="5" t="s">
+      <c r="I61" s="2">
+        <v>14</v>
+      </c>
+      <c r="J61" t="s">
         <v>259</v>
       </c>
-      <c r="I61" s="2">
-        <v>14</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="K61" s="2">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
         <v>260</v>
       </c>
-      <c r="K61" s="2">
-        <v>14</v>
-      </c>
-      <c r="L61" t="s">
+      <c r="M61" s="2">
+        <v>14</v>
+      </c>
+      <c r="N61" t="s">
         <v>261</v>
-      </c>
-      <c r="M61" s="2">
-        <v>14</v>
-      </c>
-      <c r="N61" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -4107,54 +4131,87 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
+        <v>262</v>
+      </c>
+      <c r="C62">
+        <v>14</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E62">
+        <v>14</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G62">
+        <v>14</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="I62">
+        <v>14</v>
+      </c>
+      <c r="J62" t="s">
+        <v>266</v>
+      </c>
+      <c r="K62">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>267</v>
+      </c>
+      <c r="M62">
+        <v>14</v>
+      </c>
+      <c r="N62" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C62">
-        <v>14</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E62">
-        <v>14</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="G62">
-        <v>14</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="I62">
-        <v>14</v>
-      </c>
-      <c r="J62" t="s">
-        <v>267</v>
-      </c>
-      <c r="K62">
-        <v>14</v>
-      </c>
-      <c r="L62" t="s">
-        <v>268</v>
-      </c>
-      <c r="M62">
-        <v>14</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+    </row>
+    <row r="63" spans="1:14" ht="37.5">
       <c r="A63">
         <v>61</v>
       </c>
+      <c r="B63" t="s">
+        <v>268</v>
+      </c>
       <c r="C63">
         <v>14</v>
       </c>
+      <c r="D63" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="E63">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G63">
+        <v>14</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I63">
+        <v>14</v>
+      </c>
+      <c r="J63" t="s">
+        <v>272</v>
+      </c>
+      <c r="K63">
+        <v>10</v>
+      </c>
+      <c r="L63" t="s">
+        <v>273</v>
+      </c>
+      <c r="M63">
+        <v>10</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="64" spans="1:14">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D990137F-6C09-4796-9ED4-8808AECE754A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC55F26-E3C4-4256-9DEE-086468616668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="323">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -633,10 +633,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>簡体中国語</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>開始遊戲</t>
   </si>
   <si>
@@ -1139,6 +1135,159 @@
     <rPh sb="18" eb="19">
       <t>ナイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Начать игру</t>
+  </si>
+  <si>
+    <t>Настройки</t>
+  </si>
+  <si>
+    <t>Выход</t>
+  </si>
+  <si>
+    <t>Назад</t>
+  </si>
+  <si>
+    <t>Чувствительность</t>
+  </si>
+  <si>
+    <t>Музыка</t>
+  </si>
+  <si>
+    <t>Звуки</t>
+  </si>
+  <si>
+    <t>Яркость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Режим экрана</t>
+  </si>
+  <si>
+    <t>Полный экран</t>
+  </si>
+  <si>
+    <t>В окне</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Разрешение</t>
+  </si>
+  <si>
+    <t>Управление</t>
+  </si>
+  <si>
+    <t>Показать</t>
+  </si>
+  <si>
+    <t>Скрыть</t>
+  </si>
+  <si>
+    <t>Описание предмета</t>
+  </si>
+  <si>
+    <t>Описание компаса</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>Громкость</t>
+  </si>
+  <si>
+    <t>Экран</t>
+  </si>
+  <si>
+    <t>Подсказки</t>
+  </si>
+  <si>
+    <t>Язык</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Документы</t>
+  </si>
+  <si>
+    <t>Загадочные предметы</t>
+  </si>
+  <si>
+    <t>Продолжить</t>
+  </si>
+  <si>
+    <t>Предметы</t>
+  </si>
+  <si>
+    <t>В главное меню</t>
+  </si>
+  <si>
+    <t>Лабиринт-темница</t>
+  </si>
+  <si>
+    <t>Грёза</t>
+  </si>
+  <si>
+    <t>Морок</t>
+  </si>
+  <si>
+    <t>Кошмар</t>
+  </si>
+  <si>
+    <t>Заново</t>
+  </si>
+  <si>
+    <t>Пройти опрос —
+нажмите здесь!</t>
+  </si>
+  <si>
+    <t>В список желаемого —
+нажмите здесь!</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>繁體中文</t>
+  </si>
+  <si>
+    <t>Portuguese</t>
+  </si>
+  <si>
+    <t>Данные</t>
+  </si>
+  <si>
+    <t>Удалить данные</t>
+  </si>
+  <si>
+    <t>Скитальцы</t>
+  </si>
+  <si>
+    <t>Архив</t>
+  </si>
+  <si>
+    <t>Сдаться</t>
+  </si>
+  <si>
+    <t>К выбору этапа</t>
+  </si>
+  <si>
+    <t>Русский</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>簡体中文</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1505,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1520,10 +1669,12 @@
     <col min="11" max="11" width="21.75" customWidth="1"/>
     <col min="12" max="12" width="26" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="29.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="33.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1546,28 +1697,34 @@
         <v>134</v>
       </c>
       <c r="H1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" t="s">
         <v>163</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>164</v>
       </c>
-      <c r="J1" t="s">
-        <v>165</v>
-      </c>
       <c r="K1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M1" t="s">
-        <v>200</v>
-      </c>
-      <c r="N1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="N1" t="s">
+        <v>274</v>
+      </c>
+      <c r="O1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1590,25 +1747,31 @@
         <v>14</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I2" s="5">
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K2">
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="N2" t="s">
+        <v>276</v>
+      </c>
+      <c r="O2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1631,28 +1794,34 @@
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="5">
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K3">
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M3">
         <v>14</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" t="s">
+        <v>277</v>
+      </c>
+      <c r="O3">
+        <v>11</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1675,25 +1844,31 @@
         <v>14</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I4" s="5">
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K4">
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M4">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4" t="s">
+        <v>278</v>
+      </c>
+      <c r="O4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1722,22 +1897,28 @@
         <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K5">
         <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M5">
         <v>24</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" t="s">
+        <v>279</v>
+      </c>
+      <c r="O5">
+        <v>24</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1760,28 +1941,34 @@
         <v>14</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I6" s="5">
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K6">
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M6">
         <v>12</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O6">
+        <v>9</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1821,8 +2008,14 @@
       <c r="M7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7" t="s">
+        <v>281</v>
+      </c>
+      <c r="O7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1862,8 +2055,14 @@
       <c r="M8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8" t="s">
+        <v>282</v>
+      </c>
+      <c r="O8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1892,19 +2091,25 @@
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K9">
         <v>12</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="37.5">
+      <c r="N9" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1927,25 +2132,31 @@
         <v>10</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I10" s="5">
         <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="O10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1974,19 +2185,25 @@
         <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K11">
         <v>12</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2009,25 +2226,31 @@
         <v>16</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I12" s="5">
         <v>16</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K12">
         <v>16</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="37.5">
+      <c r="N12" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2050,25 +2273,31 @@
         <v>10</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I13" s="5">
         <v>10</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="37.5">
+      <c r="N13" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="O13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2091,28 +2320,34 @@
         <v>10</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I14" s="5">
         <v>10</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K14">
         <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="O14">
+        <v>8</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:16">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2135,28 +2370,34 @@
         <v>16</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I15" s="5">
         <v>16</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K15">
         <v>14</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M15">
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O15">
+        <v>13</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:16">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2179,28 +2420,34 @@
         <v>16</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I16" s="5">
         <v>16</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K16">
         <v>14</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M16">
         <v>14</v>
       </c>
       <c r="N16" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O16">
+        <v>14</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="37.5">
+    <row r="17" spans="1:16" ht="37.5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2223,25 +2470,31 @@
         <v>10</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I17" s="5">
         <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K17">
         <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="37.5">
+      <c r="N17" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="O17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2264,66 +2517,78 @@
         <v>10</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I18" s="5">
         <v>10</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="N18" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="O18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E19">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G19" s="2">
         <v>16</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I19" s="5">
         <v>16</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K19">
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="N19" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="O19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2363,8 +2628,14 @@
       <c r="M20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="N20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="37.5">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2387,28 +2658,34 @@
         <v>24</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I21" s="5">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K21">
         <v>18</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M21">
         <v>18</v>
       </c>
       <c r="N21" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="O21">
+        <v>13</v>
+      </c>
+      <c r="P21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2431,28 +2708,34 @@
         <v>24</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I22" s="5">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K22">
         <v>18</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M22">
         <v>18</v>
       </c>
       <c r="N22" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="O22">
+        <v>15</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2481,22 +2764,28 @@
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K23">
         <v>18</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M23">
         <v>18</v>
       </c>
       <c r="N23" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O23">
+        <v>18</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2519,25 +2808,31 @@
         <v>24</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I24" s="5">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K24">
         <v>18</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M24">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="N24" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="O24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2560,25 +2855,31 @@
         <v>24</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I25" s="5">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K25">
         <v>18</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M25">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="N25" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="O25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2601,25 +2902,31 @@
         <v>24</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I26" s="5">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K26">
         <v>18</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="37.5">
+      <c r="N26" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2648,22 +2955,28 @@
         <v>32</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K27">
         <v>32</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M27">
         <v>32</v>
       </c>
       <c r="N27" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O27">
+        <v>32</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="37.5">
+    <row r="28" spans="1:16" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2692,22 +3005,28 @@
         <v>32</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K28">
         <v>32</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M28">
         <v>32</v>
       </c>
       <c r="N28" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="O28">
+        <v>32</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="37.5">
+    <row r="29" spans="1:16" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2736,22 +3055,28 @@
         <v>14</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K29">
         <v>14</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M29">
         <v>14</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="37.5">
+        <v>298</v>
+      </c>
+      <c r="O29">
+        <v>14</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="37.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2780,22 +3105,28 @@
         <v>14</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K30">
         <v>14</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M30">
         <v>14</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>299</v>
+      </c>
+      <c r="O30">
+        <v>14</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2824,22 +3155,28 @@
         <v>12</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K31">
         <v>12</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M31">
         <v>12</v>
       </c>
       <c r="N31" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="O31">
+        <v>12</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:16">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2862,28 +3199,34 @@
         <v>14</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I32" s="5">
         <v>14</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K32">
         <v>14</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M32">
         <v>14</v>
       </c>
       <c r="N32" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="O32">
+        <v>13</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="75">
+    <row r="33" spans="1:16" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2912,22 +3255,28 @@
         <v>14</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K33">
         <v>14</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M33">
         <v>14</v>
       </c>
       <c r="N33" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="O33">
+        <v>14</v>
+      </c>
+      <c r="P33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:16" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -2956,22 +3305,28 @@
         <v>14</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K34">
         <v>12</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M34">
         <v>14</v>
       </c>
       <c r="N34" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="O34">
+        <v>10</v>
+      </c>
+      <c r="P34" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:16">
       <c r="A35">
         <v>33</v>
       </c>
@@ -2994,28 +3349,34 @@
         <v>14</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I35" s="5">
         <v>14</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K35">
         <v>14</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M35">
         <v>14</v>
       </c>
       <c r="N35" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="O35">
+        <v>11</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:16">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3038,28 +3399,34 @@
         <v>14</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I36" s="5">
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K36">
         <v>12</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M36">
         <v>12</v>
       </c>
       <c r="N36" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="O36">
+        <v>12</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="37.5">
+    <row r="37" spans="1:16" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3082,28 +3449,34 @@
         <v>14</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I37" s="5">
         <v>14</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K37">
         <v>14</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M37">
         <v>14</v>
       </c>
       <c r="N37" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O37">
+        <v>14</v>
+      </c>
+      <c r="P37" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="37.5">
+    <row r="38" spans="1:16" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3126,28 +3499,34 @@
         <v>20</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I38" s="5">
         <v>20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K38">
         <v>12</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M38">
         <v>12</v>
       </c>
       <c r="N38" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="O38">
+        <v>12</v>
+      </c>
+      <c r="P38" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:16">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3170,25 +3549,31 @@
         <v>14</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I39" s="5">
         <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K39">
         <v>14</v>
       </c>
       <c r="L39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M39">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="N39" t="s">
+        <v>306</v>
+      </c>
+      <c r="O39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3211,25 +3596,31 @@
         <v>14</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I40" s="5">
         <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K40">
         <v>14</v>
       </c>
       <c r="L40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M40">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="N40" t="s">
+        <v>307</v>
+      </c>
+      <c r="O40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3252,25 +3643,31 @@
         <v>14</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I41" s="5">
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K41">
         <v>14</v>
       </c>
       <c r="L41" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M41">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="N41" t="s">
+        <v>308</v>
+      </c>
+      <c r="O41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3299,22 +3696,28 @@
         <v>20</v>
       </c>
       <c r="J42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K42">
         <v>16</v>
       </c>
       <c r="L42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M42">
         <v>16</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="N42" t="s">
+        <v>279</v>
+      </c>
+      <c r="O42">
+        <v>16</v>
+      </c>
+      <c r="P42" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:16">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3337,28 +3740,34 @@
         <v>14</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I43" s="5">
         <v>14</v>
       </c>
       <c r="J43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K43">
         <v>14</v>
       </c>
       <c r="L43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M43">
         <v>14</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="N43" t="s">
+        <v>309</v>
+      </c>
+      <c r="O43">
+        <v>14</v>
+      </c>
+      <c r="P43" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3381,28 +3790,34 @@
         <v>20</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>20</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K44">
         <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M44">
         <v>20</v>
       </c>
       <c r="N44" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O44">
+        <v>20</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="37.5">
+    <row r="45" spans="1:16" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3425,25 +3840,31 @@
         <v>10</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I45" s="5">
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K45">
         <v>8</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M45">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="56.25">
+      <c r="N45" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="O45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="56.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3466,25 +3887,31 @@
         <v>10</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I46" s="5">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K46">
         <v>8</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M46">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="37.5">
+      <c r="N46" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="O46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3507,28 +3934,34 @@
         <v>16</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I47" s="5">
         <v>16</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K47">
         <v>16</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M47">
         <v>16</v>
       </c>
       <c r="N47" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O47">
+        <v>15</v>
+      </c>
+      <c r="P47" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="37.5">
+    <row r="48" spans="1:16" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3551,28 +3984,34 @@
         <v>16</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I48" s="5">
         <v>16</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K48">
         <v>16</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M48">
         <v>16</v>
       </c>
       <c r="N48" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O48">
+        <v>16</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="37.5">
+    <row r="49" spans="1:16" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -3595,28 +4034,34 @@
         <v>16</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I49" s="5">
         <v>16</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K49">
         <v>14</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M49">
         <v>14</v>
       </c>
       <c r="N49" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="O49">
+        <v>13</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="37.5">
+    <row r="50" spans="1:16" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -3639,233 +4084,269 @@
         <v>16</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I50" s="5">
         <v>16</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K50">
         <v>14</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M50">
         <v>14</v>
       </c>
       <c r="N50" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="O50">
+        <v>14</v>
+      </c>
+      <c r="P50" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>322</v>
       </c>
       <c r="C51">
         <v>14</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E51">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G51">
         <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I51">
         <v>14</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K51">
         <v>14</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M51">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="N51" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="O51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C52">
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E52">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G52">
         <v>14</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I52">
         <v>14</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K52">
         <v>14</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M52">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="N52" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C53">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G53">
         <v>14</v>
       </c>
       <c r="H53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I53">
         <v>14</v>
       </c>
       <c r="J53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K53">
         <v>14</v>
       </c>
       <c r="L53" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="N53" t="s">
+        <v>198</v>
+      </c>
+      <c r="O53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C54">
         <v>14</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E54">
         <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G54">
         <v>14</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I54">
         <v>14</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K54">
         <v>14</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M54">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="N54" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="O54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55">
+        <v>14</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C55">
-        <v>14</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55">
+        <v>14</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E55">
-        <v>14</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
         <v>237</v>
       </c>
-      <c r="G55">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="I55">
+        <v>14</v>
+      </c>
+      <c r="J55" t="s">
         <v>238</v>
       </c>
-      <c r="I55">
-        <v>14</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="K55">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
         <v>239</v>
       </c>
-      <c r="K55">
-        <v>14</v>
-      </c>
-      <c r="L55" t="s">
-        <v>240</v>
-      </c>
       <c r="M55">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="37.5">
+      <c r="N55" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -3894,63 +4375,75 @@
         <v>24</v>
       </c>
       <c r="J56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K56">
         <v>24</v>
       </c>
       <c r="L56" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M56">
         <v>24</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="N56" t="s">
+        <v>279</v>
+      </c>
+      <c r="O56">
+        <v>24</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57">
+        <v>14</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E57">
+        <v>14</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C57">
-        <v>14</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E57">
-        <v>14</v>
-      </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
         <v>244</v>
       </c>
-      <c r="G57">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
         <v>245</v>
-      </c>
-      <c r="I57">
-        <v>14</v>
-      </c>
-      <c r="J57" t="s">
-        <v>246</v>
       </c>
       <c r="K57">
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M57">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="N57" t="s">
+        <v>316</v>
+      </c>
+      <c r="O57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58">
         <v>56</v>
       </c>
@@ -3979,22 +4472,28 @@
         <v>14</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K58">
         <v>14</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M58">
         <v>14</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
+        <v>298</v>
+      </c>
+      <c r="O58">
+        <v>14</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4023,205 +4522,271 @@
         <v>14</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K59">
         <v>14</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M59">
         <v>14</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+        <v>299</v>
+      </c>
+      <c r="O59">
+        <v>14</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C60">
-        <v>16</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E60">
-        <v>16</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2">
+        <v>16</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="I60" s="5">
+        <v>16</v>
+      </c>
+      <c r="J60" t="s">
         <v>251</v>
       </c>
-      <c r="G60" s="2">
-        <v>16</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="I60" s="5">
-        <v>16</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="K60">
+        <v>16</v>
+      </c>
+      <c r="L60" t="s">
         <v>252</v>
       </c>
-      <c r="K60">
-        <v>16</v>
-      </c>
-      <c r="L60" t="s">
+      <c r="M60">
+        <v>16</v>
+      </c>
+      <c r="N60" t="s">
+        <v>317</v>
+      </c>
+      <c r="O60">
+        <v>13</v>
+      </c>
+      <c r="P60" t="s">
         <v>253</v>
       </c>
-      <c r="M60">
-        <v>16</v>
-      </c>
-      <c r="N60" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>254</v>
+      </c>
+      <c r="C61">
+        <v>14</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C61">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61">
+        <v>14</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="E61">
-        <v>14</v>
-      </c>
-      <c r="F61" s="8" t="s">
+      <c r="G61" s="2">
+        <v>14</v>
+      </c>
+      <c r="H61" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G61" s="2">
-        <v>14</v>
-      </c>
-      <c r="H61" s="5" t="s">
+      <c r="I61" s="2">
+        <v>14</v>
+      </c>
+      <c r="J61" t="s">
         <v>258</v>
       </c>
-      <c r="I61" s="2">
-        <v>14</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="K61" s="2">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
         <v>259</v>
       </c>
-      <c r="K61" s="2">
-        <v>14</v>
-      </c>
-      <c r="L61" t="s">
+      <c r="M61" s="2">
+        <v>14</v>
+      </c>
+      <c r="N61" t="s">
+        <v>318</v>
+      </c>
+      <c r="O61" s="2">
+        <v>14</v>
+      </c>
+      <c r="P61" t="s">
         <v>260</v>
       </c>
-      <c r="M61" s="2">
-        <v>14</v>
-      </c>
-      <c r="N61" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" t="s">
+        <v>261</v>
+      </c>
+      <c r="C62">
+        <v>14</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E62">
+        <v>14</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G62">
+        <v>14</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I62">
+        <v>14</v>
+      </c>
+      <c r="J62" t="s">
+        <v>265</v>
+      </c>
+      <c r="K62">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>266</v>
+      </c>
+      <c r="M62">
+        <v>14</v>
+      </c>
+      <c r="N62" t="s">
+        <v>319</v>
+      </c>
+      <c r="O62">
+        <v>14</v>
+      </c>
+      <c r="P62" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C62">
-        <v>14</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E62">
-        <v>14</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G62">
-        <v>14</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I62">
-        <v>14</v>
-      </c>
-      <c r="J62" t="s">
-        <v>266</v>
-      </c>
-      <c r="K62">
-        <v>14</v>
-      </c>
-      <c r="L62" t="s">
-        <v>267</v>
-      </c>
-      <c r="M62">
-        <v>14</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="37.5">
+    </row>
+    <row r="63" spans="1:16" ht="37.5">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" t="s">
+        <v>267</v>
+      </c>
+      <c r="C63">
+        <v>14</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="C63">
-        <v>14</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="E63">
         <v>12</v>
       </c>
       <c r="F63" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="G63">
+        <v>14</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G63">
-        <v>14</v>
-      </c>
-      <c r="H63" s="5" t="s">
+      <c r="I63">
+        <v>14</v>
+      </c>
+      <c r="J63" t="s">
         <v>271</v>
-      </c>
-      <c r="I63">
-        <v>14</v>
-      </c>
-      <c r="J63" t="s">
-        <v>272</v>
       </c>
       <c r="K63">
         <v>10</v>
       </c>
       <c r="L63" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M63">
         <v>10</v>
       </c>
-      <c r="N63" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="N63" t="s">
+        <v>320</v>
+      </c>
+      <c r="O63">
+        <v>10</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64">
         <v>62</v>
       </c>
+      <c r="B64" t="s">
+        <v>321</v>
+      </c>
       <c r="C64">
         <v>14</v>
       </c>
+      <c r="D64" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="E64">
+        <v>14</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G64">
+        <v>14</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I64">
+        <v>14</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="K64">
+        <v>14</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="M64">
+        <v>14</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="O64">
         <v>14</v>
       </c>
     </row>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC55F26-E3C4-4256-9DEE-086468616668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DECCE6-9E0A-4952-861F-C719A96BECC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="321">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -932,10 +932,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>简体中文</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>繁體中文</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1254,9 +1250,6 @@
   <si>
     <t>В список желаемого —
 нажмите здесь!</t>
-  </si>
-  <si>
-    <t>简体中文</t>
   </si>
   <si>
     <t>繁體中文</t>
@@ -1715,10 +1708,10 @@
         <v>199</v>
       </c>
       <c r="N1" t="s">
+        <v>273</v>
+      </c>
+      <c r="O1" t="s">
         <v>274</v>
-      </c>
-      <c r="O1" t="s">
-        <v>275</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>49</v>
@@ -1765,7 +1758,7 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O2">
         <v>14</v>
@@ -1812,7 +1805,7 @@
         <v>14</v>
       </c>
       <c r="N3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O3">
         <v>11</v>
@@ -1862,7 +1855,7 @@
         <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O4">
         <v>14</v>
@@ -1909,7 +1902,7 @@
         <v>24</v>
       </c>
       <c r="N5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O5">
         <v>24</v>
@@ -1959,7 +1952,7 @@
         <v>12</v>
       </c>
       <c r="N6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -2009,7 +2002,7 @@
         <v>14</v>
       </c>
       <c r="N7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O7">
         <v>14</v>
@@ -2056,7 +2049,7 @@
         <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O8">
         <v>14</v>
@@ -2103,7 +2096,7 @@
         <v>12</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O9">
         <v>12</v>
@@ -2150,7 +2143,7 @@
         <v>8</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -2197,7 +2190,7 @@
         <v>12</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O11">
         <v>12</v>
@@ -2244,7 +2237,7 @@
         <v>16</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O12">
         <v>16</v>
@@ -2291,7 +2284,7 @@
         <v>10</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O13">
         <v>9</v>
@@ -2338,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -2388,7 +2381,7 @@
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O15">
         <v>13</v>
@@ -2438,7 +2431,7 @@
         <v>14</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O16">
         <v>14</v>
@@ -2447,7 +2440,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="37.5">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2488,7 +2481,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -2535,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -2546,43 +2539,43 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19">
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E19">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G19" s="2">
         <v>16</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I19" s="5">
         <v>16</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K19">
         <v>16</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M19">
         <v>16</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O19">
         <v>16</v>
@@ -2635,7 +2628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="37.5">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2676,7 +2669,7 @@
         <v>18</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O21">
         <v>13</v>
@@ -2726,7 +2719,7 @@
         <v>18</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O22">
         <v>15</v>
@@ -2776,7 +2769,7 @@
         <v>18</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O23">
         <v>18</v>
@@ -2826,7 +2819,7 @@
         <v>18</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O24">
         <v>18</v>
@@ -2873,7 +2866,7 @@
         <v>18</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O25">
         <v>18</v>
@@ -2920,7 +2913,7 @@
         <v>18</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O26">
         <v>18</v>
@@ -2967,7 +2960,7 @@
         <v>32</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O27">
         <v>32</v>
@@ -3017,7 +3010,7 @@
         <v>32</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O28">
         <v>32</v>
@@ -3067,13 +3060,13 @@
         <v>14</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O29">
         <v>14</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="37.5">
@@ -3117,13 +3110,13 @@
         <v>14</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O30">
         <v>14</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3167,7 +3160,7 @@
         <v>12</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O31">
         <v>12</v>
@@ -3217,7 +3210,7 @@
         <v>14</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O32">
         <v>13</v>
@@ -3267,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O33">
         <v>14</v>
@@ -3317,7 +3310,7 @@
         <v>14</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3367,7 +3360,7 @@
         <v>14</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O35">
         <v>11</v>
@@ -3417,7 +3410,7 @@
         <v>12</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O36">
         <v>12</v>
@@ -3467,7 +3460,7 @@
         <v>14</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O37">
         <v>14</v>
@@ -3517,7 +3510,7 @@
         <v>12</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O38">
         <v>12</v>
@@ -3567,7 +3560,7 @@
         <v>14</v>
       </c>
       <c r="N39" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O39">
         <v>14</v>
@@ -3614,7 +3607,7 @@
         <v>14</v>
       </c>
       <c r="N40" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O40">
         <v>14</v>
@@ -3661,7 +3654,7 @@
         <v>14</v>
       </c>
       <c r="N41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O41">
         <v>14</v>
@@ -3708,7 +3701,7 @@
         <v>16</v>
       </c>
       <c r="N42" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O42">
         <v>16</v>
@@ -3758,7 +3751,7 @@
         <v>14</v>
       </c>
       <c r="N43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O43">
         <v>14</v>
@@ -3808,7 +3801,7 @@
         <v>20</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O44">
         <v>20</v>
@@ -3858,7 +3851,7 @@
         <v>8</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O45">
         <v>8</v>
@@ -3905,7 +3898,7 @@
         <v>8</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O46">
         <v>8</v>
@@ -3952,7 +3945,7 @@
         <v>16</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O47">
         <v>15</v>
@@ -4002,7 +3995,7 @@
         <v>16</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O48">
         <v>16</v>
@@ -4052,7 +4045,7 @@
         <v>14</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O49">
         <v>13</v>
@@ -4102,7 +4095,7 @@
         <v>14</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O50">
         <v>14</v>
@@ -4116,43 +4109,43 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C51">
         <v>14</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="E51">
         <v>14</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="G51">
         <v>14</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="I51">
         <v>14</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="K51">
         <v>14</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="M51">
         <v>14</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="O51">
         <v>14</v>
@@ -4163,43 +4156,43 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C52">
         <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E52">
         <v>14</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G52">
         <v>14</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I52">
         <v>14</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K52">
         <v>14</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M52">
         <v>14</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O52">
         <v>14</v>
@@ -4293,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O54">
         <v>14</v>
@@ -4304,43 +4297,43 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>233</v>
+      </c>
+      <c r="C55">
+        <v>14</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C55">
-        <v>14</v>
-      </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55">
+        <v>14</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E55">
-        <v>14</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55">
+        <v>14</v>
+      </c>
+      <c r="H55" t="s">
         <v>236</v>
       </c>
-      <c r="G55">
-        <v>14</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="I55">
+        <v>14</v>
+      </c>
+      <c r="J55" t="s">
         <v>237</v>
       </c>
-      <c r="I55">
-        <v>14</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="K55">
+        <v>14</v>
+      </c>
+      <c r="L55" t="s">
         <v>238</v>
       </c>
-      <c r="K55">
-        <v>14</v>
-      </c>
-      <c r="L55" t="s">
-        <v>239</v>
-      </c>
       <c r="M55">
         <v>14</v>
       </c>
       <c r="N55" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O55">
         <v>14</v>
@@ -4387,13 +4380,13 @@
         <v>24</v>
       </c>
       <c r="N56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O56">
         <v>24</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4401,43 +4394,43 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>241</v>
+      </c>
+      <c r="C57">
+        <v>14</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E57">
+        <v>14</v>
+      </c>
+      <c r="F57" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C57">
-        <v>14</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E57">
-        <v>14</v>
-      </c>
-      <c r="F57" s="8" t="s">
+      <c r="G57">
+        <v>14</v>
+      </c>
+      <c r="H57" t="s">
         <v>243</v>
       </c>
-      <c r="G57">
-        <v>14</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="I57">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
         <v>244</v>
-      </c>
-      <c r="I57">
-        <v>14</v>
-      </c>
-      <c r="J57" t="s">
-        <v>245</v>
       </c>
       <c r="K57">
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M57">
         <v>12</v>
       </c>
       <c r="N57" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="O57">
         <v>12</v>
@@ -4484,13 +4477,13 @@
         <v>14</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O58">
         <v>14</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4534,13 +4527,13 @@
         <v>14</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O59">
         <v>14</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4548,49 +4541,49 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
+        <v>247</v>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C60">
-        <v>16</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60">
+        <v>16</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E60">
-        <v>16</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="2">
+        <v>16</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I60" s="5">
+        <v>16</v>
+      </c>
+      <c r="J60" t="s">
         <v>250</v>
       </c>
-      <c r="G60" s="2">
-        <v>16</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="I60" s="5">
-        <v>16</v>
-      </c>
-      <c r="J60" t="s">
+      <c r="K60">
+        <v>16</v>
+      </c>
+      <c r="L60" t="s">
         <v>251</v>
       </c>
-      <c r="K60">
-        <v>16</v>
-      </c>
-      <c r="L60" t="s">
-        <v>252</v>
-      </c>
       <c r="M60">
         <v>16</v>
       </c>
       <c r="N60" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="O60">
         <v>13</v>
       </c>
       <c r="P60" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4598,49 +4591,49 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>253</v>
+      </c>
+      <c r="C61">
+        <v>14</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C61">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61">
+        <v>14</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E61">
-        <v>14</v>
-      </c>
-      <c r="F61" s="8" t="s">
+      <c r="G61" s="2">
+        <v>14</v>
+      </c>
+      <c r="H61" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G61" s="2">
-        <v>14</v>
-      </c>
-      <c r="H61" s="5" t="s">
+      <c r="I61" s="2">
+        <v>14</v>
+      </c>
+      <c r="J61" t="s">
         <v>257</v>
       </c>
-      <c r="I61" s="2">
-        <v>14</v>
-      </c>
-      <c r="J61" t="s">
+      <c r="K61" s="2">
+        <v>14</v>
+      </c>
+      <c r="L61" t="s">
         <v>258</v>
       </c>
-      <c r="K61" s="2">
-        <v>14</v>
-      </c>
-      <c r="L61" t="s">
+      <c r="M61" s="2">
+        <v>14</v>
+      </c>
+      <c r="N61" t="s">
+        <v>316</v>
+      </c>
+      <c r="O61" s="2">
+        <v>14</v>
+      </c>
+      <c r="P61" t="s">
         <v>259</v>
-      </c>
-      <c r="M61" s="2">
-        <v>14</v>
-      </c>
-      <c r="N61" t="s">
-        <v>318</v>
-      </c>
-      <c r="O61" s="2">
-        <v>14</v>
-      </c>
-      <c r="P61" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4648,49 +4641,49 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62">
+        <v>14</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E62">
+        <v>14</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G62">
+        <v>14</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I62">
+        <v>14</v>
+      </c>
+      <c r="J62" t="s">
+        <v>264</v>
+      </c>
+      <c r="K62">
+        <v>14</v>
+      </c>
+      <c r="L62" t="s">
+        <v>265</v>
+      </c>
+      <c r="M62">
+        <v>14</v>
+      </c>
+      <c r="N62" t="s">
+        <v>317</v>
+      </c>
+      <c r="O62">
+        <v>14</v>
+      </c>
+      <c r="P62" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C62">
-        <v>14</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E62">
-        <v>14</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G62">
-        <v>14</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I62">
-        <v>14</v>
-      </c>
-      <c r="J62" t="s">
-        <v>265</v>
-      </c>
-      <c r="K62">
-        <v>14</v>
-      </c>
-      <c r="L62" t="s">
-        <v>266</v>
-      </c>
-      <c r="M62">
-        <v>14</v>
-      </c>
-      <c r="N62" t="s">
-        <v>319</v>
-      </c>
-      <c r="O62">
-        <v>14</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="37.5">
@@ -4698,49 +4691,49 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63">
+        <v>14</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="C63">
-        <v>14</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="E63">
         <v>12</v>
       </c>
       <c r="F63" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G63">
+        <v>14</v>
+      </c>
+      <c r="H63" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G63">
-        <v>14</v>
-      </c>
-      <c r="H63" s="5" t="s">
+      <c r="I63">
+        <v>14</v>
+      </c>
+      <c r="J63" t="s">
         <v>270</v>
-      </c>
-      <c r="I63">
-        <v>14</v>
-      </c>
-      <c r="J63" t="s">
-        <v>271</v>
       </c>
       <c r="K63">
         <v>10</v>
       </c>
       <c r="L63" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M63">
         <v>10</v>
       </c>
       <c r="N63" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="O63">
         <v>10</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4748,46 +4741,46 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M64">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="O64">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DECCE6-9E0A-4952-861F-C719A96BECC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618CE803-626F-4DBD-9DA2-D1CA339500F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4744,43 +4744,43 @@
         <v>319</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>319</v>
       </c>
       <c r="E64">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>319</v>
       </c>
       <c r="G64">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>319</v>
       </c>
       <c r="I64">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>319</v>
       </c>
       <c r="K64">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L64" s="1" t="s">
         <v>319</v>
       </c>
       <c r="M64">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N64" s="1" t="s">
         <v>319</v>
       </c>
       <c r="O64">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:5">

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618CE803-626F-4DBD-9DA2-D1CA339500F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0175F4-1BD0-45D0-87A6-9B3DA0C31B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="366">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1281,6 +1281,146 @@
   </si>
   <si>
     <t>簡体中文</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Spiel starten</t>
+  </si>
+  <si>
+    <t>Optionen</t>
+  </si>
+  <si>
+    <t>Beenden</t>
+  </si>
+  <si>
+    <t>Zurück</t>
+  </si>
+  <si>
+    <t>Empfindlichkeit</t>
+  </si>
+  <si>
+    <t>Musik</t>
+  </si>
+  <si>
+    <t>Effekte</t>
+  </si>
+  <si>
+    <t>Helligkeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Bildschirmmodus</t>
+  </si>
+  <si>
+    <t>Vollbild</t>
+  </si>
+  <si>
+    <t>Fenster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Auflösung</t>
+  </si>
+  <si>
+    <t>Steuerung</t>
+  </si>
+  <si>
+    <t>Anzeigen</t>
+  </si>
+  <si>
+    <t>Ausblenden</t>
+  </si>
+  <si>
+    <t>Gegenstandsinfo</t>
+  </si>
+  <si>
+    <t>Kompassinfo</t>
+  </si>
+  <si>
+    <t>Lautstärke</t>
+  </si>
+  <si>
+    <t>Bildschirm</t>
+  </si>
+  <si>
+    <t>Erklärungen</t>
+  </si>
+  <si>
+    <t>Sprache</t>
+  </si>
+  <si>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>Nein</t>
+  </si>
+  <si>
+    <t>Dokumente</t>
+  </si>
+  <si>
+    <t>Mysteriöse Gegenstände</t>
+  </si>
+  <si>
+    <t>Fortsetzen</t>
+  </si>
+  <si>
+    <t>Gegenstände</t>
+  </si>
+  <si>
+    <t>Zum Titelbildschirm</t>
+  </si>
+  <si>
+    <t>Kerkerlabyrinth</t>
+  </si>
+  <si>
+    <t>Träumerei</t>
+  </si>
+  <si>
+    <t>Trugbild</t>
+  </si>
+  <si>
+    <t>Albtraum</t>
+  </si>
+  <si>
+    <t>Neustart</t>
+  </si>
+  <si>
+    <t>Hier klicken
+zur Umfrage!</t>
+  </si>
+  <si>
+    <t>Hier klicken für
+die Wunschliste!</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>Daten</t>
+  </si>
+  <si>
+    <t>Daten löschen</t>
+  </si>
+  <si>
+    <t>Umherirrende</t>
+  </si>
+  <si>
+    <t>Archiv</t>
+  </si>
+  <si>
+    <t>Aufgeben</t>
+  </si>
+  <si>
+    <t>Zur Stufenauswahl</t>
+  </si>
+  <si>
+    <t>German</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1647,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1664,10 +1804,12 @@
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="33.875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1713,11 +1855,17 @@
       <c r="O1" t="s">
         <v>274</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>322</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1763,8 +1911,14 @@
       <c r="O2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="P2" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1810,11 +1964,17 @@
       <c r="O3">
         <v>11</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q3">
+        <v>13</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1860,8 +2020,14 @@
       <c r="O4">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="P4" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1907,11 +2073,17 @@
       <c r="O5">
         <v>24</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q5">
+        <v>24</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1957,11 +2129,17 @@
       <c r="O6">
         <v>9</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="P6" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q6">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2007,8 +2185,14 @@
       <c r="O7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="P7" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2054,8 +2238,14 @@
       <c r="O8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="P8" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2101,8 +2291,14 @@
       <c r="O9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="37.5">
+      <c r="P9" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2148,8 +2344,14 @@
       <c r="O10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="P10" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2195,8 +2397,14 @@
       <c r="O11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="P11" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2242,8 +2450,14 @@
       <c r="O12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="37.5">
+      <c r="P12" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2289,8 +2503,14 @@
       <c r="O13">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="37.5">
+      <c r="P13" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2337,10 +2557,16 @@
         <v>8</v>
       </c>
       <c r="P14" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q14">
+        <v>8</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2387,10 +2613,16 @@
         <v>13</v>
       </c>
       <c r="P15" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q15">
+        <v>13</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2437,10 +2669,16 @@
         <v>14</v>
       </c>
       <c r="P16" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q16">
+        <v>10</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2486,8 +2724,14 @@
       <c r="O17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="37.5">
+      <c r="P17" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2533,8 +2777,14 @@
       <c r="O18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="P18" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2580,8 +2830,14 @@
       <c r="O19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="P19" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2627,8 +2883,14 @@
       <c r="O20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="P20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2675,10 +2937,16 @@
         <v>13</v>
       </c>
       <c r="P21" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q21">
+        <v>15</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2725,10 +2993,16 @@
         <v>15</v>
       </c>
       <c r="P22" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q22">
+        <v>14</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2775,10 +3049,16 @@
         <v>18</v>
       </c>
       <c r="P23" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q23">
+        <v>17</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2824,8 +3104,14 @@
       <c r="O24">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="P24" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2871,8 +3157,14 @@
       <c r="O25">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="P25" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2918,8 +3210,14 @@
       <c r="O26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="37.5">
+      <c r="P26" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2966,10 +3264,16 @@
         <v>32</v>
       </c>
       <c r="P27" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q27">
+        <v>32</v>
+      </c>
+      <c r="R27" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="37.5">
+    <row r="28" spans="1:18" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3016,10 +3320,16 @@
         <v>32</v>
       </c>
       <c r="P28" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q28">
+        <v>32</v>
+      </c>
+      <c r="R28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="37.5">
+    <row r="29" spans="1:18" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3066,10 +3376,16 @@
         <v>14</v>
       </c>
       <c r="P29" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q29">
+        <v>14</v>
+      </c>
+      <c r="R29" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="37.5">
+    <row r="30" spans="1:18" ht="37.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3116,10 +3432,16 @@
         <v>14</v>
       </c>
       <c r="P30" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q30">
+        <v>14</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:18">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3166,10 +3488,16 @@
         <v>12</v>
       </c>
       <c r="P31" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q31">
+        <v>11</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:18">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3216,10 +3544,16 @@
         <v>13</v>
       </c>
       <c r="P32" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q32">
+        <v>13</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="75">
+    <row r="33" spans="1:18" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3266,10 +3600,16 @@
         <v>14</v>
       </c>
       <c r="P33" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q33">
+        <v>14</v>
+      </c>
+      <c r="R33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="37.5">
+    <row r="34" spans="1:18" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3316,10 +3656,16 @@
         <v>10</v>
       </c>
       <c r="P34" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q34">
+        <v>9</v>
+      </c>
+      <c r="R34" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3366,10 +3712,16 @@
         <v>11</v>
       </c>
       <c r="P35" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q35">
+        <v>12</v>
+      </c>
+      <c r="R35" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:18">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3416,10 +3768,16 @@
         <v>12</v>
       </c>
       <c r="P36" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q36">
+        <v>12</v>
+      </c>
+      <c r="R36" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="37.5">
+    <row r="37" spans="1:18" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3466,10 +3824,16 @@
         <v>14</v>
       </c>
       <c r="P37" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q37">
+        <v>11</v>
+      </c>
+      <c r="R37" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="37.5">
+    <row r="38" spans="1:18" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3516,10 +3880,16 @@
         <v>12</v>
       </c>
       <c r="P38" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q38">
+        <v>12</v>
+      </c>
+      <c r="R38" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:18">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3565,8 +3935,14 @@
       <c r="O39">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="P39" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3612,8 +3988,14 @@
       <c r="O40">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="P40" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q40">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3659,8 +4041,14 @@
       <c r="O41">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="P41" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3706,11 +4094,17 @@
       <c r="O42">
         <v>16</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="P42" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q42">
+        <v>16</v>
+      </c>
+      <c r="R42" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:18">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3756,11 +4150,17 @@
       <c r="O43">
         <v>14</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="P43" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q43">
+        <v>14</v>
+      </c>
+      <c r="R43" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:18">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3807,10 +4207,16 @@
         <v>20</v>
       </c>
       <c r="P44" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q44">
+        <v>16</v>
+      </c>
+      <c r="R44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="37.5">
+    <row r="45" spans="1:18" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3856,8 +4262,14 @@
       <c r="O45">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="56.25">
+      <c r="P45" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="56.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3903,8 +4315,14 @@
       <c r="O46">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="37.5">
+      <c r="P46" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3951,10 +4369,16 @@
         <v>15</v>
       </c>
       <c r="P47" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q47">
+        <v>15</v>
+      </c>
+      <c r="R47" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="37.5">
+    <row r="48" spans="1:18" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4001,10 +4425,16 @@
         <v>16</v>
       </c>
       <c r="P48" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q48">
+        <v>12</v>
+      </c>
+      <c r="R48" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="37.5">
+    <row r="49" spans="1:18" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4051,10 +4481,16 @@
         <v>13</v>
       </c>
       <c r="P49" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q49">
+        <v>13</v>
+      </c>
+      <c r="R49" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="37.5">
+    <row r="50" spans="1:18" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4101,10 +4537,16 @@
         <v>14</v>
       </c>
       <c r="P50" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q50">
+        <v>10</v>
+      </c>
+      <c r="R50" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:18">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4150,8 +4592,14 @@
       <c r="O51">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:16">
+      <c r="P51" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4197,8 +4645,14 @@
       <c r="O52">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:16">
+      <c r="P52" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4244,8 +4698,14 @@
       <c r="O53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="P53" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4291,8 +4751,14 @@
       <c r="O54">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="P54" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4338,8 +4804,14 @@
       <c r="O55">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="37.5">
+      <c r="P55" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4385,11 +4857,17 @@
       <c r="O56">
         <v>24</v>
       </c>
-      <c r="P56" s="1" t="s">
+      <c r="P56" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q56">
+        <v>24</v>
+      </c>
+      <c r="R56" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:18">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4435,8 +4913,14 @@
       <c r="O57">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="P57" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4483,10 +4967,16 @@
         <v>14</v>
       </c>
       <c r="P58" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q58">
+        <v>14</v>
+      </c>
+      <c r="R58" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:18">
       <c r="A59">
         <v>57</v>
       </c>
@@ -4533,10 +5023,16 @@
         <v>14</v>
       </c>
       <c r="P59" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q59">
+        <v>14</v>
+      </c>
+      <c r="R59" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:18">
       <c r="A60">
         <v>58</v>
       </c>
@@ -4583,10 +5079,16 @@
         <v>13</v>
       </c>
       <c r="P60" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q60">
+        <v>10</v>
+      </c>
+      <c r="R60" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:18">
       <c r="A61">
         <v>59</v>
       </c>
@@ -4633,10 +5135,16 @@
         <v>14</v>
       </c>
       <c r="P61" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>14</v>
+      </c>
+      <c r="R61" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:18">
       <c r="A62">
         <v>60</v>
       </c>
@@ -4682,11 +5190,17 @@
       <c r="O62">
         <v>14</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="P62" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q62">
+        <v>14</v>
+      </c>
+      <c r="R62" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="37.5">
+    <row r="63" spans="1:18" ht="37.5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -4732,11 +5246,17 @@
       <c r="O63">
         <v>10</v>
       </c>
-      <c r="P63" s="1" t="s">
+      <c r="P63" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q63">
+        <v>10</v>
+      </c>
+      <c r="R63" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:18">
       <c r="A64">
         <v>62</v>
       </c>
@@ -4782,19 +5302,67 @@
       <c r="O64">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="P64" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q64">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65">
         <v>63</v>
       </c>
+      <c r="B65" t="s">
+        <v>365</v>
+      </c>
       <c r="C65">
         <v>14</v>
       </c>
+      <c r="D65" t="s">
+        <v>365</v>
+      </c>
       <c r="E65">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" t="s">
+        <v>365</v>
+      </c>
+      <c r="G65">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s">
+        <v>365</v>
+      </c>
+      <c r="I65">
+        <v>14</v>
+      </c>
+      <c r="J65" t="s">
+        <v>365</v>
+      </c>
+      <c r="K65">
+        <v>14</v>
+      </c>
+      <c r="L65" t="s">
+        <v>365</v>
+      </c>
+      <c r="M65">
+        <v>14</v>
+      </c>
+      <c r="N65" t="s">
+        <v>365</v>
+      </c>
+      <c r="O65">
+        <v>14</v>
+      </c>
+      <c r="P65" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q65">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66">
         <v>64</v>
       </c>
@@ -4805,7 +5373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:17">
       <c r="A67">
         <v>65</v>
       </c>
@@ -4816,7 +5384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:17">
       <c r="A68">
         <v>66</v>
       </c>
@@ -4827,7 +5395,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:17">
       <c r="A69">
         <v>67</v>
       </c>
@@ -4838,7 +5406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:17">
       <c r="A70">
         <v>68</v>
       </c>
@@ -4849,7 +5417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:17">
       <c r="A71">
         <v>69</v>
       </c>
@@ -4860,7 +5428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:17">
       <c r="A72">
         <v>70</v>
       </c>
@@ -4871,7 +5439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:17">
       <c r="A73">
         <v>71</v>
       </c>
@@ -4882,7 +5450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:17">
       <c r="A74">
         <v>72</v>
       </c>
@@ -4893,7 +5461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:17">
       <c r="A75">
         <v>73</v>
       </c>
@@ -4904,7 +5472,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:17">
       <c r="A76">
         <v>74</v>
       </c>
@@ -4915,7 +5483,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:17">
       <c r="A77">
         <v>75</v>
       </c>
@@ -4926,7 +5494,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:17">
       <c r="A78">
         <v>76</v>
       </c>
@@ -4937,7 +5505,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:17">
       <c r="A79">
         <v>77</v>
       </c>
@@ -4948,7 +5516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:17">
       <c r="A80">
         <v>78</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0175F4-1BD0-45D0-87A6-9B3DA0C31B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D771342F-802B-4E60-9FEE-E123F1975DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1397,9 +1397,6 @@
   <si>
     <t>Hier klicken für
 die Wunschliste!</t>
-  </si>
-  <si>
-    <t>简体中文</t>
   </si>
   <si>
     <t>Daten</t>
@@ -4593,7 +4590,7 @@
         <v>14</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="Q51">
         <v>14</v>
@@ -4805,7 +4802,7 @@
         <v>14</v>
       </c>
       <c r="P55" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q55">
         <v>14</v>
@@ -4914,7 +4911,7 @@
         <v>12</v>
       </c>
       <c r="P57" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q57">
         <v>12</v>
@@ -5079,7 +5076,7 @@
         <v>13</v>
       </c>
       <c r="P60" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q60">
         <v>10</v>
@@ -5135,7 +5132,7 @@
         <v>14</v>
       </c>
       <c r="P61" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q61" s="2">
         <v>14</v>
@@ -5191,7 +5188,7 @@
         <v>14</v>
       </c>
       <c r="P62" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q62">
         <v>14</v>
@@ -5247,7 +5244,7 @@
         <v>10</v>
       </c>
       <c r="P63" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q63">
         <v>10</v>
@@ -5314,49 +5311,49 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C65">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E65">
         <v>14</v>
       </c>
       <c r="F65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G65">
         <v>14</v>
       </c>
       <c r="H65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I65">
         <v>14</v>
       </c>
       <c r="J65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K65">
         <v>14</v>
       </c>
       <c r="L65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M65">
         <v>14</v>
       </c>
       <c r="N65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O65">
         <v>14</v>
       </c>
       <c r="P65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q65">
         <v>14</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D771342F-802B-4E60-9FEE-E123F1975DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773FAAB5-76D9-4531-A60B-B305C16F74A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="410">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1418,6 +1418,146 @@
   </si>
   <si>
     <t>German</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>Commencer</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Quitter</t>
+  </si>
+  <si>
+    <t>Retour</t>
+  </si>
+  <si>
+    <t>Sensibilité</t>
+  </si>
+  <si>
+    <t>Musique</t>
+  </si>
+  <si>
+    <t>Effets</t>
+  </si>
+  <si>
+    <t>Luminosité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Mode d'affichage</t>
+  </si>
+  <si>
+    <t>Plein écran</t>
+  </si>
+  <si>
+    <t>Fenêtré</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Résolution</t>
+  </si>
+  <si>
+    <t>Commandes</t>
+  </si>
+  <si>
+    <t>Afficher</t>
+  </si>
+  <si>
+    <t>Masquer</t>
+  </si>
+  <si>
+    <t>Description d'objet</t>
+  </si>
+  <si>
+    <t>Description boussole</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Écran</t>
+  </si>
+  <si>
+    <t>Explications</t>
+  </si>
+  <si>
+    <t>Langue</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Objets mystérieux</t>
+  </si>
+  <si>
+    <t>Continuer</t>
+  </si>
+  <si>
+    <t>Objets</t>
+  </si>
+  <si>
+    <t>Retour au titre</t>
+  </si>
+  <si>
+    <t>Labyrinthe-prison</t>
+  </si>
+  <si>
+    <t>Rêverie</t>
+  </si>
+  <si>
+    <t>Chimère</t>
+  </si>
+  <si>
+    <t>Cauchemar</t>
+  </si>
+  <si>
+    <t>Recommencer</t>
+  </si>
+  <si>
+    <t>Cliquez ici pour
+le questionnaire !</t>
+  </si>
+  <si>
+    <t>Cliquez ici pour
+la liste de souhaits !</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>Données</t>
+  </si>
+  <si>
+    <t>Supprimer les données</t>
+  </si>
+  <si>
+    <t>Errants</t>
+  </si>
+  <si>
+    <t>Archives</t>
+  </si>
+  <si>
+    <t>Abandonner</t>
+  </si>
+  <si>
+    <t>Retour à la sélection</t>
+  </si>
+  <si>
+    <t>French</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1784,7 +1924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:T102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1803,10 +1943,12 @@
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.25" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1858,11 +2000,17 @@
       <c r="Q1" t="s">
         <v>322</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
+        <v>365</v>
+      </c>
+      <c r="S1" t="s">
+        <v>366</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1914,8 +2062,14 @@
       <c r="Q2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
+      <c r="R2" t="s">
+        <v>367</v>
+      </c>
+      <c r="S2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1967,11 +2121,17 @@
       <c r="Q3">
         <v>13</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" t="s">
+        <v>368</v>
+      </c>
+      <c r="S3">
+        <v>14</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2023,8 +2183,14 @@
       <c r="Q4">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="R4" t="s">
+        <v>369</v>
+      </c>
+      <c r="S4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2076,11 +2242,17 @@
       <c r="Q5">
         <v>24</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" t="s">
+        <v>370</v>
+      </c>
+      <c r="S5">
+        <v>24</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2132,11 +2304,17 @@
       <c r="Q6">
         <v>10</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" t="s">
+        <v>371</v>
+      </c>
+      <c r="S6">
+        <v>12</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2188,8 +2366,14 @@
       <c r="Q7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="R7" t="s">
+        <v>372</v>
+      </c>
+      <c r="S7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2241,8 +2425,14 @@
       <c r="Q8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="R8" t="s">
+        <v>373</v>
+      </c>
+      <c r="S8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2294,8 +2484,14 @@
       <c r="Q9">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="37.5">
+      <c r="R9" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="S9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2347,8 +2543,14 @@
       <c r="Q10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="R10" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="S10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2400,8 +2602,14 @@
       <c r="Q11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="R11" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="S11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2453,8 +2661,14 @@
       <c r="Q12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="37.5">
+      <c r="R12" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="S12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2506,8 +2720,14 @@
       <c r="Q13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="37.5">
+      <c r="R13" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="S13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2560,10 +2780,16 @@
         <v>8</v>
       </c>
       <c r="R14" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="S14">
+        <v>8</v>
+      </c>
+      <c r="T14" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2616,10 +2842,16 @@
         <v>13</v>
       </c>
       <c r="R15" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S15">
+        <v>13</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2672,10 +2904,16 @@
         <v>10</v>
       </c>
       <c r="R16" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S16">
+        <v>14</v>
+      </c>
+      <c r="T16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2727,8 +2965,14 @@
       <c r="Q17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="37.5">
+      <c r="R17" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="S17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2780,8 +3024,14 @@
       <c r="Q18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:18">
+      <c r="R18" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="S18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2833,8 +3083,14 @@
       <c r="Q19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="R19" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="S19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2886,8 +3142,14 @@
       <c r="Q20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="R20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2940,10 +3202,16 @@
         <v>15</v>
       </c>
       <c r="R21" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="S21">
+        <v>18</v>
+      </c>
+      <c r="T21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:20">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2996,10 +3264,16 @@
         <v>14</v>
       </c>
       <c r="R22" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="S22">
+        <v>18</v>
+      </c>
+      <c r="T22" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:20">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3052,10 +3326,16 @@
         <v>17</v>
       </c>
       <c r="R23" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="S23">
+        <v>17</v>
+      </c>
+      <c r="T23" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3107,8 +3387,14 @@
       <c r="Q24">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="R24" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="S24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3160,8 +3446,14 @@
       <c r="Q25">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="R25" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="S25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3213,8 +3505,14 @@
       <c r="Q26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" ht="37.5">
+      <c r="R26" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="S26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3267,10 +3565,16 @@
         <v>32</v>
       </c>
       <c r="R27" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="S27">
+        <v>32</v>
+      </c>
+      <c r="T27" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="37.5">
+    <row r="28" spans="1:20" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3323,10 +3627,16 @@
         <v>32</v>
       </c>
       <c r="R28" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="S28">
+        <v>32</v>
+      </c>
+      <c r="T28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="37.5">
+    <row r="29" spans="1:20" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3379,10 +3689,16 @@
         <v>14</v>
       </c>
       <c r="R29" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="S29">
+        <v>14</v>
+      </c>
+      <c r="T29" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="37.5">
+    <row r="30" spans="1:20" ht="37.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3435,10 +3751,16 @@
         <v>14</v>
       </c>
       <c r="R30" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="S30">
+        <v>14</v>
+      </c>
+      <c r="T30" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:20">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3491,10 +3813,16 @@
         <v>11</v>
       </c>
       <c r="R31" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="S31">
+        <v>11</v>
+      </c>
+      <c r="T31" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:20">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3547,10 +3875,16 @@
         <v>13</v>
       </c>
       <c r="R32" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="S32">
+        <v>13</v>
+      </c>
+      <c r="T32" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="75">
+    <row r="33" spans="1:20" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3603,10 +3937,16 @@
         <v>14</v>
       </c>
       <c r="R33" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="S33">
+        <v>14</v>
+      </c>
+      <c r="T33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="37.5">
+    <row r="34" spans="1:20" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3659,10 +3999,16 @@
         <v>9</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="S34">
+        <v>12</v>
+      </c>
+      <c r="T34" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:20">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3715,10 +4061,16 @@
         <v>12</v>
       </c>
       <c r="R35" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="S35">
+        <v>13</v>
+      </c>
+      <c r="T35" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:20">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3771,10 +4123,16 @@
         <v>12</v>
       </c>
       <c r="R36" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="S36">
+        <v>12</v>
+      </c>
+      <c r="T36" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="37.5">
+    <row r="37" spans="1:20" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3827,10 +4185,16 @@
         <v>11</v>
       </c>
       <c r="R37" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="S37">
+        <v>14</v>
+      </c>
+      <c r="T37" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="37.5">
+    <row r="38" spans="1:20" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3883,10 +4247,16 @@
         <v>12</v>
       </c>
       <c r="R38" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="S38">
+        <v>12</v>
+      </c>
+      <c r="T38" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:20">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3938,8 +4308,14 @@
       <c r="Q39">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="R39" t="s">
+        <v>396</v>
+      </c>
+      <c r="S39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3991,8 +4367,14 @@
       <c r="Q40">
         <v>13</v>
       </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="R40" t="s">
+        <v>397</v>
+      </c>
+      <c r="S40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4044,8 +4426,14 @@
       <c r="Q41">
         <v>14</v>
       </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="R41" t="s">
+        <v>398</v>
+      </c>
+      <c r="S41">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4097,11 +4485,17 @@
       <c r="Q42">
         <v>16</v>
       </c>
-      <c r="R42" s="1" t="s">
+      <c r="R42" t="s">
+        <v>370</v>
+      </c>
+      <c r="S42">
+        <v>16</v>
+      </c>
+      <c r="T42" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:20">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4153,11 +4547,17 @@
       <c r="Q43">
         <v>14</v>
       </c>
-      <c r="R43" s="1" t="s">
+      <c r="R43" t="s">
+        <v>399</v>
+      </c>
+      <c r="S43">
+        <v>11</v>
+      </c>
+      <c r="T43" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:20">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4210,10 +4610,16 @@
         <v>16</v>
       </c>
       <c r="R44" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="S44">
+        <v>20</v>
+      </c>
+      <c r="T44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="37.5">
+    <row r="45" spans="1:20" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4265,8 +4671,14 @@
       <c r="Q45">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" ht="56.25">
+      <c r="R45" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="S45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="56.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4318,8 +4730,14 @@
       <c r="Q46">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" ht="37.5">
+      <c r="R46" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="S46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4372,10 +4790,16 @@
         <v>15</v>
       </c>
       <c r="R47" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S47">
+        <v>15</v>
+      </c>
+      <c r="T47" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="37.5">
+    <row r="48" spans="1:20" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4428,10 +4852,16 @@
         <v>12</v>
       </c>
       <c r="R48" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S48">
+        <v>16</v>
+      </c>
+      <c r="T48" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="37.5">
+    <row r="49" spans="1:20" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4484,10 +4914,16 @@
         <v>13</v>
       </c>
       <c r="R49" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="S49">
+        <v>13</v>
+      </c>
+      <c r="T49" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="37.5">
+    <row r="50" spans="1:20" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4540,10 +4976,16 @@
         <v>10</v>
       </c>
       <c r="R50" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="S50">
+        <v>14</v>
+      </c>
+      <c r="T50" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:20">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4595,8 +5037,14 @@
       <c r="Q51">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="R51" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="S51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4648,8 +5096,14 @@
       <c r="Q52">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="R52" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="S52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4701,8 +5155,14 @@
       <c r="Q53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="R53" t="s">
+        <v>198</v>
+      </c>
+      <c r="S53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4754,8 +5214,14 @@
       <c r="Q54">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="R54" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="S54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4807,8 +5273,14 @@
       <c r="Q55">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" ht="37.5">
+      <c r="R55" t="s">
+        <v>403</v>
+      </c>
+      <c r="S55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4860,11 +5332,17 @@
       <c r="Q56">
         <v>24</v>
       </c>
-      <c r="R56" s="1" t="s">
+      <c r="R56" t="s">
+        <v>370</v>
+      </c>
+      <c r="S56">
+        <v>24</v>
+      </c>
+      <c r="T56" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:20">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4916,8 +5394,14 @@
       <c r="Q57">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="R57" t="s">
+        <v>404</v>
+      </c>
+      <c r="S57">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4970,10 +5454,16 @@
         <v>14</v>
       </c>
       <c r="R58" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="S58">
+        <v>14</v>
+      </c>
+      <c r="T58" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:20">
       <c r="A59">
         <v>57</v>
       </c>
@@ -5026,10 +5516,16 @@
         <v>14</v>
       </c>
       <c r="R59" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="S59">
+        <v>14</v>
+      </c>
+      <c r="T59" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:20">
       <c r="A60">
         <v>58</v>
       </c>
@@ -5082,10 +5578,16 @@
         <v>10</v>
       </c>
       <c r="R60" t="s">
+        <v>405</v>
+      </c>
+      <c r="S60">
+        <v>16</v>
+      </c>
+      <c r="T60" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:20">
       <c r="A61">
         <v>59</v>
       </c>
@@ -5138,10 +5640,16 @@
         <v>14</v>
       </c>
       <c r="R61" t="s">
+        <v>406</v>
+      </c>
+      <c r="S61" s="2">
+        <v>13</v>
+      </c>
+      <c r="T61" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:18">
+    <row r="62" spans="1:20">
       <c r="A62">
         <v>60</v>
       </c>
@@ -5193,11 +5701,17 @@
       <c r="Q62">
         <v>14</v>
       </c>
-      <c r="R62" s="1" t="s">
+      <c r="R62" t="s">
+        <v>407</v>
+      </c>
+      <c r="S62">
+        <v>12</v>
+      </c>
+      <c r="T62" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="37.5">
+    <row r="63" spans="1:20" ht="37.5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -5249,11 +5763,17 @@
       <c r="Q63">
         <v>10</v>
       </c>
-      <c r="R63" s="1" t="s">
+      <c r="R63" t="s">
+        <v>408</v>
+      </c>
+      <c r="S63">
+        <v>10</v>
+      </c>
+      <c r="T63" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:20">
       <c r="A64">
         <v>62</v>
       </c>
@@ -5305,8 +5825,14 @@
       <c r="Q64">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:17">
+      <c r="R64" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="S64">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>63</v>
       </c>
@@ -5358,19 +5884,73 @@
       <c r="Q65">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:17">
+      <c r="R65" t="s">
+        <v>364</v>
+      </c>
+      <c r="S65">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>64</v>
       </c>
+      <c r="B66" t="s">
+        <v>409</v>
+      </c>
       <c r="C66">
         <v>14</v>
       </c>
+      <c r="D66" t="s">
+        <v>409</v>
+      </c>
       <c r="E66">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" spans="1:17">
+      <c r="F66" t="s">
+        <v>409</v>
+      </c>
+      <c r="G66">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s">
+        <v>409</v>
+      </c>
+      <c r="I66">
+        <v>14</v>
+      </c>
+      <c r="J66" t="s">
+        <v>409</v>
+      </c>
+      <c r="K66">
+        <v>14</v>
+      </c>
+      <c r="L66" t="s">
+        <v>409</v>
+      </c>
+      <c r="M66">
+        <v>14</v>
+      </c>
+      <c r="N66" t="s">
+        <v>409</v>
+      </c>
+      <c r="O66">
+        <v>14</v>
+      </c>
+      <c r="P66" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q66">
+        <v>14</v>
+      </c>
+      <c r="R66" t="s">
+        <v>409</v>
+      </c>
+      <c r="S66">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>65</v>
       </c>
@@ -5381,7 +5961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>66</v>
       </c>
@@ -5392,7 +5972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>67</v>
       </c>
@@ -5403,7 +5983,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>68</v>
       </c>
@@ -5414,7 +5994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>69</v>
       </c>
@@ -5425,7 +6005,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>70</v>
       </c>
@@ -5436,7 +6016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>71</v>
       </c>
@@ -5447,7 +6027,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:17">
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>72</v>
       </c>
@@ -5458,7 +6038,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:17">
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>73</v>
       </c>
@@ -5469,7 +6049,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:17">
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>74</v>
       </c>
@@ -5480,7 +6060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:17">
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>75</v>
       </c>
@@ -5491,7 +6071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:17">
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>76</v>
       </c>
@@ -5502,7 +6082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:17">
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>77</v>
       </c>
@@ -5513,7 +6093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:17">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>78</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773FAAB5-76D9-4531-A60B-B305C16F74A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17C1A74-1A5C-4083-AA40-CE58B27A2366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="409">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1534,9 +1534,6 @@
   <si>
     <t>Cliquez ici pour
 la liste de souhaits !</t>
-  </si>
-  <si>
-    <t>简体中文</t>
   </si>
   <si>
     <t>Données</t>
@@ -5038,7 +5035,7 @@
         <v>14</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>402</v>
+        <v>320</v>
       </c>
       <c r="S51">
         <v>14</v>
@@ -5274,7 +5271,7 @@
         <v>14</v>
       </c>
       <c r="R55" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="S55">
         <v>14</v>
@@ -5395,7 +5392,7 @@
         <v>12</v>
       </c>
       <c r="R57" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="S57">
         <v>11</v>
@@ -5578,7 +5575,7 @@
         <v>10</v>
       </c>
       <c r="R60" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="S60">
         <v>16</v>
@@ -5640,7 +5637,7 @@
         <v>14</v>
       </c>
       <c r="R61" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="S61" s="2">
         <v>13</v>
@@ -5702,7 +5699,7 @@
         <v>14</v>
       </c>
       <c r="R62" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="S62">
         <v>12</v>
@@ -5764,7 +5761,7 @@
         <v>10</v>
       </c>
       <c r="R63" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="S63">
         <v>10</v>
@@ -5896,55 +5893,55 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C66">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E66">
         <v>14</v>
       </c>
       <c r="F66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G66">
         <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I66">
         <v>14</v>
       </c>
       <c r="J66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K66">
         <v>14</v>
       </c>
       <c r="L66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M66">
         <v>14</v>
       </c>
       <c r="N66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O66">
         <v>14</v>
       </c>
       <c r="P66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q66">
         <v>14</v>
       </c>
       <c r="R66" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="S66">
         <v>14</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17C1A74-1A5C-4083-AA40-CE58B27A2366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569B6E58-C206-4AEB-BAB5-95170CAB11E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="453">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1555,6 +1555,143 @@
   </si>
   <si>
     <t>French</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Oyuna Başla</t>
+  </si>
+  <si>
+    <t>Ayarlar</t>
+  </si>
+  <si>
+    <t>Çıkış</t>
+  </si>
+  <si>
+    <t>Geri</t>
+  </si>
+  <si>
+    <t>Hassasiyet</t>
+  </si>
+  <si>
+    <t>Müzik</t>
+  </si>
+  <si>
+    <t>Efektler</t>
+  </si>
+  <si>
+    <t>Parlaklık</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Ekran modu</t>
+  </si>
+  <si>
+    <t>Tam ekran</t>
+  </si>
+  <si>
+    <t>Pencere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Çözünürlük</t>
+  </si>
+  <si>
+    <t>Kontroller</t>
+  </si>
+  <si>
+    <t>Göster</t>
+  </si>
+  <si>
+    <t>Gizle</t>
+  </si>
+  <si>
+    <t>Eşya açıklaması</t>
+  </si>
+  <si>
+    <t>Pusula açıklaması</t>
+  </si>
+  <si>
+    <t>Ses</t>
+  </si>
+  <si>
+    <t>Ekran</t>
+  </si>
+  <si>
+    <t>Açıklamalar</t>
+  </si>
+  <si>
+    <t>Dil</t>
+  </si>
+  <si>
+    <t>Evet</t>
+  </si>
+  <si>
+    <t>Hayır</t>
+  </si>
+  <si>
+    <t>Belgeler</t>
+  </si>
+  <si>
+    <t>Gizemli Eşyalar</t>
+  </si>
+  <si>
+    <t>Devam Et</t>
+  </si>
+  <si>
+    <t>Eşyalar</t>
+  </si>
+  <si>
+    <t>Ana Menüye Dön</t>
+  </si>
+  <si>
+    <t>Zindan Labirenti</t>
+  </si>
+  <si>
+    <t>Hayal</t>
+  </si>
+  <si>
+    <t>Serap</t>
+  </si>
+  <si>
+    <t>Kâbus</t>
+  </si>
+  <si>
+    <t>Yeniden Başla</t>
+  </si>
+  <si>
+    <t>Anket için
+buraya tıklayın!</t>
+  </si>
+  <si>
+    <t>İstek listesi için
+buraya tıklayın!</t>
+  </si>
+  <si>
+    <t>Veri</t>
+  </si>
+  <si>
+    <t>Veriyi Sil</t>
+  </si>
+  <si>
+    <t>Gezginler</t>
+  </si>
+  <si>
+    <t>Arşiv</t>
+  </si>
+  <si>
+    <t>Vazgeç</t>
+  </si>
+  <si>
+    <t>Bölüm Seçimine Dön</t>
+  </si>
+  <si>
+    <t>Turkish</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1921,7 +2058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T102"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="51.25" customWidth="1"/>
@@ -1942,10 +2079,12 @@
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="29.25" style="1" customWidth="1"/>
+    <col min="20" max="20" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2003,11 +2142,17 @@
       <c r="S1" t="s">
         <v>366</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
+        <v>409</v>
+      </c>
+      <c r="U1" t="s">
+        <v>410</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2065,8 +2210,14 @@
       <c r="S2">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="T2" t="s">
+        <v>411</v>
+      </c>
+      <c r="U2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2124,11 +2275,17 @@
       <c r="S3">
         <v>14</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" t="s">
+        <v>412</v>
+      </c>
+      <c r="U3">
+        <v>14</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2186,8 +2343,14 @@
       <c r="S4">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="T4" t="s">
+        <v>413</v>
+      </c>
+      <c r="U4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2245,11 +2408,17 @@
       <c r="S5">
         <v>24</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" t="s">
+        <v>414</v>
+      </c>
+      <c r="U5">
+        <v>24</v>
+      </c>
+      <c r="V5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2307,11 +2476,17 @@
       <c r="S6">
         <v>12</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="T6" t="s">
+        <v>415</v>
+      </c>
+      <c r="U6">
+        <v>12</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2369,8 +2544,14 @@
       <c r="S7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="T7" t="s">
+        <v>416</v>
+      </c>
+      <c r="U7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2428,8 +2609,14 @@
       <c r="S8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="T8" t="s">
+        <v>417</v>
+      </c>
+      <c r="U8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2487,8 +2674,14 @@
       <c r="S9">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="37.5">
+      <c r="T9" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="U9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="37.5">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2546,8 +2739,14 @@
       <c r="S10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="T10" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2605,8 +2804,14 @@
       <c r="S11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="T11" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="U11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2664,8 +2869,14 @@
       <c r="S12">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="37.5">
+      <c r="T12" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="U12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2723,8 +2934,14 @@
       <c r="S13">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="37.5">
+      <c r="T13" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="U13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2783,10 +3000,16 @@
         <v>8</v>
       </c>
       <c r="T14" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="U14">
+        <v>8</v>
+      </c>
+      <c r="V14" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:22">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2845,10 +3068,16 @@
         <v>13</v>
       </c>
       <c r="T15" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="U15">
+        <v>14</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2907,10 +3136,16 @@
         <v>14</v>
       </c>
       <c r="T16" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="U16">
+        <v>14</v>
+      </c>
+      <c r="V16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:22">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2968,8 +3203,14 @@
       <c r="S17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="37.5">
+      <c r="T17" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="U17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="37.5">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3027,8 +3268,14 @@
       <c r="S18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="T18" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="U18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3086,8 +3333,14 @@
       <c r="S19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="T19" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3145,8 +3398,14 @@
       <c r="S20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="T20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="U20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3205,10 +3464,16 @@
         <v>18</v>
       </c>
       <c r="T21" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="U21">
+        <v>18</v>
+      </c>
+      <c r="V21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:22">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3267,10 +3532,16 @@
         <v>18</v>
       </c>
       <c r="T22" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="U22">
+        <v>18</v>
+      </c>
+      <c r="V22" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:22">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3329,10 +3600,16 @@
         <v>17</v>
       </c>
       <c r="T23" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="U23">
+        <v>18</v>
+      </c>
+      <c r="V23" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:22">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3390,8 +3667,14 @@
       <c r="S24">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="T24" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="U24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3449,8 +3732,14 @@
       <c r="S25">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="T25" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="U25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3508,8 +3797,14 @@
       <c r="S26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="37.5">
+      <c r="T26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="U26">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="37.5">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3568,10 +3863,16 @@
         <v>32</v>
       </c>
       <c r="T27" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="U27">
+        <v>32</v>
+      </c>
+      <c r="V27" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="37.5">
+    <row r="28" spans="1:22" ht="37.5">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3630,10 +3931,16 @@
         <v>32</v>
       </c>
       <c r="T28" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="U28">
+        <v>32</v>
+      </c>
+      <c r="V28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="37.5">
+    <row r="29" spans="1:22" ht="37.5">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3692,10 +3999,16 @@
         <v>14</v>
       </c>
       <c r="T29" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="U29">
+        <v>14</v>
+      </c>
+      <c r="V29" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="37.5">
+    <row r="30" spans="1:22" ht="37.5">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3754,10 +4067,16 @@
         <v>14</v>
       </c>
       <c r="T30" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="U30">
+        <v>14</v>
+      </c>
+      <c r="V30" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:22">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3816,10 +4135,16 @@
         <v>11</v>
       </c>
       <c r="T31" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="U31">
+        <v>12</v>
+      </c>
+      <c r="V31" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:22">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3878,10 +4203,16 @@
         <v>13</v>
       </c>
       <c r="T32" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="U32">
+        <v>14</v>
+      </c>
+      <c r="V32" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="75">
+    <row r="33" spans="1:22" ht="75">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3940,10 +4271,16 @@
         <v>14</v>
       </c>
       <c r="T33" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="U33">
+        <v>14</v>
+      </c>
+      <c r="V33" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="37.5">
+    <row r="34" spans="1:22" ht="37.5">
       <c r="A34">
         <v>32</v>
       </c>
@@ -4002,10 +4339,16 @@
         <v>12</v>
       </c>
       <c r="T34" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="U34">
+        <v>13</v>
+      </c>
+      <c r="V34" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:22">
       <c r="A35">
         <v>33</v>
       </c>
@@ -4064,10 +4407,16 @@
         <v>13</v>
       </c>
       <c r="T35" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="U35">
+        <v>14</v>
+      </c>
+      <c r="V35" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:22">
       <c r="A36">
         <v>34</v>
       </c>
@@ -4126,10 +4475,16 @@
         <v>12</v>
       </c>
       <c r="T36" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="U36">
+        <v>12</v>
+      </c>
+      <c r="V36" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="37.5">
+    <row r="37" spans="1:22" ht="37.5">
       <c r="A37">
         <v>35</v>
       </c>
@@ -4188,10 +4543,16 @@
         <v>14</v>
       </c>
       <c r="T37" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="U37">
+        <v>14</v>
+      </c>
+      <c r="V37" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="37.5">
+    <row r="38" spans="1:22" ht="37.5">
       <c r="A38">
         <v>36</v>
       </c>
@@ -4250,10 +4611,16 @@
         <v>12</v>
       </c>
       <c r="T38" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="U38">
+        <v>12</v>
+      </c>
+      <c r="V38" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:22">
       <c r="A39">
         <v>37</v>
       </c>
@@ -4311,8 +4678,14 @@
       <c r="S39">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:20">
+      <c r="T39" t="s">
+        <v>440</v>
+      </c>
+      <c r="U39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40">
         <v>38</v>
       </c>
@@ -4370,8 +4743,14 @@
       <c r="S40">
         <v>14</v>
       </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="T40" t="s">
+        <v>441</v>
+      </c>
+      <c r="U40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41">
         <v>39</v>
       </c>
@@ -4429,8 +4808,14 @@
       <c r="S41">
         <v>13</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="T41" t="s">
+        <v>442</v>
+      </c>
+      <c r="U41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42">
         <v>40</v>
       </c>
@@ -4488,11 +4873,17 @@
       <c r="S42">
         <v>16</v>
       </c>
-      <c r="T42" s="1" t="s">
+      <c r="T42" t="s">
+        <v>414</v>
+      </c>
+      <c r="U42">
+        <v>16</v>
+      </c>
+      <c r="V42" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:22">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4550,11 +4941,17 @@
       <c r="S43">
         <v>11</v>
       </c>
-      <c r="T43" s="1" t="s">
+      <c r="T43" t="s">
+        <v>443</v>
+      </c>
+      <c r="U43">
+        <v>9</v>
+      </c>
+      <c r="V43" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:22">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4613,10 +5010,16 @@
         <v>20</v>
       </c>
       <c r="T44" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="U44">
+        <v>20</v>
+      </c>
+      <c r="V44" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="37.5">
+    <row r="45" spans="1:22" ht="37.5">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4674,8 +5077,14 @@
       <c r="S45">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" ht="56.25">
+      <c r="T45" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="U45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="56.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4733,8 +5142,14 @@
       <c r="S46">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" ht="37.5">
+      <c r="T46" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="U46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="37.5">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4793,10 +5208,16 @@
         <v>15</v>
       </c>
       <c r="T47" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="U47">
+        <v>16</v>
+      </c>
+      <c r="V47" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="37.5">
+    <row r="48" spans="1:22" ht="37.5">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4855,10 +5276,16 @@
         <v>16</v>
       </c>
       <c r="T48" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="U48">
+        <v>16</v>
+      </c>
+      <c r="V48" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="37.5">
+    <row r="49" spans="1:22" ht="37.5">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4917,10 +5344,16 @@
         <v>13</v>
       </c>
       <c r="T49" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="U49">
+        <v>14</v>
+      </c>
+      <c r="V49" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="37.5">
+    <row r="50" spans="1:22" ht="37.5">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4979,10 +5412,16 @@
         <v>14</v>
       </c>
       <c r="T50" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="U50">
+        <v>14</v>
+      </c>
+      <c r="V50" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:22">
       <c r="A51">
         <v>49</v>
       </c>
@@ -5040,8 +5479,14 @@
       <c r="S51">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="T51" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="U51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
       <c r="A52">
         <v>50</v>
       </c>
@@ -5099,8 +5544,14 @@
       <c r="S52">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="T52" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="U52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22">
       <c r="A53">
         <v>51</v>
       </c>
@@ -5158,8 +5609,14 @@
       <c r="S53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="T53" t="s">
+        <v>198</v>
+      </c>
+      <c r="U53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22">
       <c r="A54">
         <v>52</v>
       </c>
@@ -5217,8 +5674,14 @@
       <c r="S54">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="T54" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="U54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22">
       <c r="A55">
         <v>53</v>
       </c>
@@ -5276,8 +5739,14 @@
       <c r="S55">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" ht="37.5">
+      <c r="T55" t="s">
+        <v>446</v>
+      </c>
+      <c r="U55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="37.5">
       <c r="A56">
         <v>54</v>
       </c>
@@ -5335,11 +5804,17 @@
       <c r="S56">
         <v>24</v>
       </c>
-      <c r="T56" s="1" t="s">
+      <c r="T56" t="s">
+        <v>414</v>
+      </c>
+      <c r="U56">
+        <v>24</v>
+      </c>
+      <c r="V56" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:22">
       <c r="A57">
         <v>55</v>
       </c>
@@ -5397,8 +5872,14 @@
       <c r="S57">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="1:20">
+      <c r="T57" t="s">
+        <v>447</v>
+      </c>
+      <c r="U57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22">
       <c r="A58">
         <v>56</v>
       </c>
@@ -5457,10 +5938,16 @@
         <v>14</v>
       </c>
       <c r="T58" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="U58">
+        <v>14</v>
+      </c>
+      <c r="V58" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:22">
       <c r="A59">
         <v>57</v>
       </c>
@@ -5519,10 +6006,16 @@
         <v>14</v>
       </c>
       <c r="T59" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="U59">
+        <v>14</v>
+      </c>
+      <c r="V59" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:22">
       <c r="A60">
         <v>58</v>
       </c>
@@ -5581,10 +6074,16 @@
         <v>16</v>
       </c>
       <c r="T60" t="s">
+        <v>448</v>
+      </c>
+      <c r="U60">
+        <v>13</v>
+      </c>
+      <c r="V60" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:22">
       <c r="A61">
         <v>59</v>
       </c>
@@ -5643,10 +6142,16 @@
         <v>13</v>
       </c>
       <c r="T61" t="s">
+        <v>449</v>
+      </c>
+      <c r="U61" s="2">
+        <v>14</v>
+      </c>
+      <c r="V61" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="1:22">
       <c r="A62">
         <v>60</v>
       </c>
@@ -5704,11 +6209,17 @@
       <c r="S62">
         <v>12</v>
       </c>
-      <c r="T62" s="1" t="s">
+      <c r="T62" t="s">
+        <v>450</v>
+      </c>
+      <c r="U62">
+        <v>14</v>
+      </c>
+      <c r="V62" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="37.5">
+    <row r="63" spans="1:22" ht="37.5">
       <c r="A63">
         <v>61</v>
       </c>
@@ -5766,11 +6277,17 @@
       <c r="S63">
         <v>10</v>
       </c>
-      <c r="T63" s="1" t="s">
+      <c r="T63" t="s">
+        <v>451</v>
+      </c>
+      <c r="U63">
+        <v>10</v>
+      </c>
+      <c r="V63" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:22">
       <c r="A64">
         <v>62</v>
       </c>
@@ -5828,8 +6345,14 @@
       <c r="S64">
         <v>14</v>
       </c>
-    </row>
-    <row r="65" spans="1:19">
+      <c r="T64" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="U64">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65">
         <v>63</v>
       </c>
@@ -5887,8 +6410,14 @@
       <c r="S65">
         <v>14</v>
       </c>
-    </row>
-    <row r="66" spans="1:19">
+      <c r="T65" t="s">
+        <v>364</v>
+      </c>
+      <c r="U65">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66">
         <v>64</v>
       </c>
@@ -5946,19 +6475,79 @@
       <c r="S66">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" spans="1:19">
+      <c r="T66" t="s">
+        <v>408</v>
+      </c>
+      <c r="U66">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67">
         <v>65</v>
       </c>
+      <c r="B67" t="s">
+        <v>452</v>
+      </c>
       <c r="C67">
         <v>14</v>
       </c>
+      <c r="D67" t="s">
+        <v>452</v>
+      </c>
       <c r="E67">
         <v>14</v>
       </c>
-    </row>
-    <row r="68" spans="1:19">
+      <c r="F67" t="s">
+        <v>452</v>
+      </c>
+      <c r="G67">
+        <v>14</v>
+      </c>
+      <c r="H67" t="s">
+        <v>452</v>
+      </c>
+      <c r="I67">
+        <v>14</v>
+      </c>
+      <c r="J67" t="s">
+        <v>452</v>
+      </c>
+      <c r="K67">
+        <v>14</v>
+      </c>
+      <c r="L67" t="s">
+        <v>452</v>
+      </c>
+      <c r="M67">
+        <v>14</v>
+      </c>
+      <c r="N67" t="s">
+        <v>452</v>
+      </c>
+      <c r="O67">
+        <v>14</v>
+      </c>
+      <c r="P67" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q67">
+        <v>14</v>
+      </c>
+      <c r="R67" t="s">
+        <v>452</v>
+      </c>
+      <c r="S67">
+        <v>14</v>
+      </c>
+      <c r="T67" t="s">
+        <v>452</v>
+      </c>
+      <c r="U67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68">
         <v>66</v>
       </c>
@@ -5969,7 +6558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:21">
       <c r="A69">
         <v>67</v>
       </c>
@@ -5980,7 +6569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:21">
       <c r="A70">
         <v>68</v>
       </c>
@@ -5991,7 +6580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:21">
       <c r="A71">
         <v>69</v>
       </c>
@@ -6002,7 +6591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:21">
       <c r="A72">
         <v>70</v>
       </c>
@@ -6013,7 +6602,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:21">
       <c r="A73">
         <v>71</v>
       </c>
@@ -6024,7 +6613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:21">
       <c r="A74">
         <v>72</v>
       </c>
@@ -6035,7 +6624,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:21">
       <c r="A75">
         <v>73</v>
       </c>
@@ -6046,7 +6635,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:21">
       <c r="A76">
         <v>74</v>
       </c>
@@ -6057,7 +6646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:21">
       <c r="A77">
         <v>75</v>
       </c>
@@ -6068,7 +6657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:21">
       <c r="A78">
         <v>76</v>
       </c>
@@ -6079,7 +6668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:21">
       <c r="A79">
         <v>77</v>
       </c>
@@ -6090,7 +6679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:21">
       <c r="A80">
         <v>78</v>
       </c>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569B6E58-C206-4AEB-BAB5-95170CAB11E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D9397-895C-4282-AF95-F697D20C5DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4945,7 +4945,7 @@
         <v>443</v>
       </c>
       <c r="U43">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>80</v>
@@ -5013,7 +5013,7 @@
         <v>438</v>
       </c>
       <c r="U44">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>82</v>

--- a/Assets/Originals/Excels/Button/ButtonMessage.xlsx
+++ b/Assets/Originals/Excels/Button/ButtonMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Button\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D9397-895C-4282-AF95-F697D20C5DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56112CFE-F29A-4467-A17D-52F754602C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="457">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -1692,6 +1692,28 @@
   </si>
   <si>
     <t>Turkish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ScreenAdjustmentPanel内の「-」ボタン</t>
+    <rPh sb="21" eb="22">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ScreenAdjustmentPanel内の「+」ボタン</t>
+    <rPh sb="21" eb="22">
+      <t>ナイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -6352,7 +6374,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:22">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6417,7 +6439,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:21">
+    <row r="66" spans="1:22">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6482,7 +6504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:21">
+    <row r="67" spans="1:22">
       <c r="A67">
         <v>65</v>
       </c>
@@ -6547,29 +6569,143 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:21">
+    <row r="68" spans="1:22" ht="37.5">
       <c r="A68">
         <v>66</v>
       </c>
+      <c r="B68" t="s">
+        <v>453</v>
+      </c>
       <c r="C68">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D68" t="s">
+        <v>453</v>
       </c>
       <c r="E68">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21">
+        <v>16</v>
+      </c>
+      <c r="F68" t="s">
+        <v>453</v>
+      </c>
+      <c r="G68">
+        <v>16</v>
+      </c>
+      <c r="H68" t="s">
+        <v>453</v>
+      </c>
+      <c r="I68">
+        <v>16</v>
+      </c>
+      <c r="J68" t="s">
+        <v>453</v>
+      </c>
+      <c r="K68">
+        <v>16</v>
+      </c>
+      <c r="L68" t="s">
+        <v>453</v>
+      </c>
+      <c r="M68">
+        <v>16</v>
+      </c>
+      <c r="N68" t="s">
+        <v>453</v>
+      </c>
+      <c r="O68">
+        <v>16</v>
+      </c>
+      <c r="P68" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q68">
+        <v>16</v>
+      </c>
+      <c r="R68" t="s">
+        <v>453</v>
+      </c>
+      <c r="S68">
+        <v>16</v>
+      </c>
+      <c r="T68" t="s">
+        <v>453</v>
+      </c>
+      <c r="U68">
+        <v>16</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="37.5">
       <c r="A69">
         <v>67</v>
       </c>
+      <c r="B69" t="s">
+        <v>455</v>
+      </c>
       <c r="C69">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D69" t="s">
+        <v>455</v>
       </c>
       <c r="E69">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21">
+        <v>16</v>
+      </c>
+      <c r="F69" t="s">
+        <v>455</v>
+      </c>
+      <c r="G69">
+        <v>16</v>
+      </c>
+      <c r="H69" t="s">
+        <v>455</v>
+      </c>
+      <c r="I69">
+        <v>16</v>
+      </c>
+      <c r="J69" t="s">
+        <v>455</v>
+      </c>
+      <c r="K69">
+        <v>16</v>
+      </c>
+      <c r="L69" t="s">
+        <v>455</v>
+      </c>
+      <c r="M69">
+        <v>16</v>
+      </c>
+      <c r="N69" t="s">
+        <v>455</v>
+      </c>
+      <c r="O69">
+        <v>16</v>
+      </c>
+      <c r="P69" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q69">
+        <v>16</v>
+      </c>
+      <c r="R69" t="s">
+        <v>455</v>
+      </c>
+      <c r="S69">
+        <v>16</v>
+      </c>
+      <c r="T69" t="s">
+        <v>455</v>
+      </c>
+      <c r="U69">
+        <v>16</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22">
       <c r="A70">
         <v>68</v>
       </c>
@@ -6580,7 +6716,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
+    <row r="71" spans="1:22">
       <c r="A71">
         <v>69</v>
       </c>
@@ -6591,7 +6727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="1:22">
       <c r="A72">
         <v>70</v>
       </c>
@@ -6602,7 +6738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:22">
       <c r="A73">
         <v>71</v>
       </c>
@@ -6613,7 +6749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="1:22">
       <c r="A74">
         <v>72</v>
       </c>
@@ -6624,7 +6760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:21">
+    <row r="75" spans="1:22">
       <c r="A75">
         <v>73</v>
       </c>
@@ -6635,7 +6771,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:21">
+    <row r="76" spans="1:22">
       <c r="A76">
         <v>74</v>
       </c>
@@ -6646,7 +6782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="1:22">
       <c r="A77">
         <v>75</v>
       </c>
@@ -6657,7 +6793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:21">
+    <row r="78" spans="1:22">
       <c r="A78">
         <v>76</v>
       </c>
@@ -6668,7 +6804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
+    <row r="79" spans="1:22">
       <c r="A79">
         <v>77</v>
       </c>
@@ -6679,7 +6815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:21">
+    <row r="80" spans="1:22">
       <c r="A80">
         <v>78</v>
       </c>
